--- a/research/traditional_assets/database/data/austria/austria_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_metals_mining.xlsx
@@ -1145,7 +1145,7 @@
         <v>4.28455284552845</v>
       </c>
       <c r="H2">
-        <v>2.71811846689895</v>
+        <v>2.71811846689896</v>
       </c>
       <c r="I2">
         <v>0.457125154894672</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09366816766273744</v>
+        <v>0.09347756406034688</v>
       </c>
       <c r="C2">
-        <v>1484.974284956463</v>
+        <v>1473.535951239327</v>
       </c>
       <c r="D2">
-        <v>1176.074284956463</v>
+        <v>1180.775951239327</v>
       </c>
       <c r="E2">
-        <v>-737.8</v>
+        <v>-721.66</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.14</v>
       </c>
       <c r="G2">
         <v>308.9</v>
@@ -1457,28 +1457,28 @@
         <v>117.45</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.811842</v>
       </c>
       <c r="N2">
-        <v>117.45</v>
+        <v>116.638158</v>
       </c>
       <c r="O2">
-        <v>28.188</v>
+        <v>27.99315792</v>
       </c>
       <c r="P2">
-        <v>89.262</v>
+        <v>88.64500007999999</v>
       </c>
       <c r="Q2">
-        <v>187.062</v>
+        <v>186.44500008</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09366816766273744</v>
+        <v>0.09403564046499685</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9917755368515749</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.6710074127724</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09347756406034688</v>
+        <v>0.0932869604579563</v>
       </c>
       <c r="C3">
-        <v>1473.535951239327</v>
+        <v>1462.135360705672</v>
       </c>
       <c r="D3">
-        <v>1180.775951239327</v>
+        <v>1185.515360705672</v>
       </c>
       <c r="E3">
-        <v>-721.66</v>
+        <v>-705.52</v>
       </c>
       <c r="F3">
-        <v>16.14</v>
+        <v>32.28</v>
       </c>
       <c r="G3">
         <v>308.9</v>
@@ -1539,28 +1539,28 @@
         <v>117.45</v>
       </c>
       <c r="M3">
-        <v>0.811842</v>
+        <v>1.623684</v>
       </c>
       <c r="N3">
-        <v>116.638158</v>
+        <v>115.826316</v>
       </c>
       <c r="O3">
-        <v>27.99315792</v>
+        <v>27.79831584</v>
       </c>
       <c r="P3">
-        <v>88.64500007999999</v>
+        <v>88.02800015999999</v>
       </c>
       <c r="Q3">
-        <v>186.44500008</v>
+        <v>185.82800016</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09403564046499685</v>
+        <v>0.09441061271220032</v>
       </c>
       <c r="T3">
-        <v>0.9917755368515749</v>
+        <v>0.9994853609192066</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.6710074127724</v>
+        <v>72.33550370638622</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0932869604579563</v>
+        <v>0.09309635685556573</v>
       </c>
       <c r="C4">
-        <v>1462.135360705672</v>
+        <v>1450.772969668872</v>
       </c>
       <c r="D4">
-        <v>1185.515360705672</v>
+        <v>1190.292969668872</v>
       </c>
       <c r="E4">
-        <v>-705.52</v>
+        <v>-689.38</v>
       </c>
       <c r="F4">
-        <v>32.28</v>
+        <v>48.42</v>
       </c>
       <c r="G4">
         <v>308.9</v>
@@ -1621,28 +1621,28 @@
         <v>117.45</v>
       </c>
       <c r="M4">
-        <v>1.623684</v>
+        <v>2.435526</v>
       </c>
       <c r="N4">
-        <v>115.826316</v>
+        <v>115.014474</v>
       </c>
       <c r="O4">
-        <v>27.79831584</v>
+        <v>27.60347376</v>
       </c>
       <c r="P4">
-        <v>88.02800015999999</v>
+        <v>87.41100023999999</v>
       </c>
       <c r="Q4">
-        <v>185.82800016</v>
+        <v>185.21100024</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09441061271220032</v>
+        <v>0.09479331634594407</v>
       </c>
       <c r="T4">
-        <v>0.9994853609192066</v>
+        <v>1.007354150431532</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.33550370638622</v>
+        <v>48.22366913759081</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09309635685556573</v>
+        <v>0.09290575325317518</v>
       </c>
       <c r="C5">
-        <v>1450.772969668872</v>
+        <v>1439.449241827809</v>
       </c>
       <c r="D5">
-        <v>1190.292969668872</v>
+        <v>1195.109241827809</v>
       </c>
       <c r="E5">
-        <v>-689.38</v>
+        <v>-673.24</v>
       </c>
       <c r="F5">
-        <v>48.42</v>
+        <v>64.56</v>
       </c>
       <c r="G5">
         <v>308.9</v>
@@ -1703,28 +1703,28 @@
         <v>117.45</v>
       </c>
       <c r="M5">
-        <v>2.435526</v>
+        <v>3.247368</v>
       </c>
       <c r="N5">
-        <v>115.014474</v>
+        <v>114.202632</v>
       </c>
       <c r="O5">
-        <v>27.60347376</v>
+        <v>27.40863168</v>
       </c>
       <c r="P5">
-        <v>87.41100023999999</v>
+        <v>86.79400031999999</v>
       </c>
       <c r="Q5">
-        <v>185.21100024</v>
+        <v>184.59400032</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09479331634594407</v>
+        <v>0.09518399297205749</v>
       </c>
       <c r="T5">
-        <v>1.007354150431532</v>
+        <v>1.015386873058697</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.22366913759081</v>
+        <v>36.16775185319311</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09290575325317518</v>
+        <v>0.09271514965078459</v>
       </c>
       <c r="C6">
-        <v>1439.449241827809</v>
+        <v>1428.164648416901</v>
       </c>
       <c r="D6">
-        <v>1195.109241827809</v>
+        <v>1199.964648416901</v>
       </c>
       <c r="E6">
-        <v>-673.24</v>
+        <v>-657.0999999999999</v>
       </c>
       <c r="F6">
-        <v>64.56</v>
+        <v>80.7</v>
       </c>
       <c r="G6">
         <v>308.9</v>
@@ -1785,28 +1785,28 @@
         <v>117.45</v>
       </c>
       <c r="M6">
-        <v>3.247368</v>
+        <v>4.05921</v>
       </c>
       <c r="N6">
-        <v>114.202632</v>
+        <v>113.39079</v>
       </c>
       <c r="O6">
-        <v>27.40863168</v>
+        <v>27.21378959999999</v>
       </c>
       <c r="P6">
-        <v>86.79400031999999</v>
+        <v>86.17700039999998</v>
       </c>
       <c r="Q6">
-        <v>184.59400032</v>
+        <v>183.9770004</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09518399297205749</v>
+        <v>0.09558289436924695</v>
       </c>
       <c r="T6">
-        <v>1.015386873058697</v>
+        <v>1.023588705635908</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.16775185319311</v>
+        <v>28.93420148255448</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09271514965078459</v>
+        <v>0.09252454604839405</v>
       </c>
       <c r="C7">
-        <v>1428.164648416901</v>
+        <v>1416.919668359795</v>
       </c>
       <c r="D7">
-        <v>1199.964648416901</v>
+        <v>1204.859668359795</v>
       </c>
       <c r="E7">
-        <v>-657.0999999999999</v>
+        <v>-640.9599999999999</v>
       </c>
       <c r="F7">
-        <v>80.7</v>
+        <v>96.84</v>
       </c>
       <c r="G7">
         <v>308.9</v>
@@ -1867,28 +1867,28 @@
         <v>117.45</v>
       </c>
       <c r="M7">
-        <v>4.05921</v>
+        <v>4.871052</v>
       </c>
       <c r="N7">
-        <v>113.39079</v>
+        <v>112.578948</v>
       </c>
       <c r="O7">
-        <v>27.21378959999999</v>
+        <v>27.01894751999999</v>
       </c>
       <c r="P7">
-        <v>86.17700039999998</v>
+        <v>85.56000047999999</v>
       </c>
       <c r="Q7">
-        <v>183.9770004</v>
+        <v>183.36000048</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09558289436924695</v>
+        <v>0.09599028303020643</v>
       </c>
       <c r="T7">
-        <v>1.023588705635908</v>
+        <v>1.031965045289229</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.93420148255448</v>
+        <v>24.11183456879541</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09252454604839405</v>
+        <v>0.09233394244600347</v>
       </c>
       <c r="C8">
-        <v>1416.919668359795</v>
+        <v>1405.714788426851</v>
       </c>
       <c r="D8">
-        <v>1204.859668359795</v>
+        <v>1209.794788426851</v>
       </c>
       <c r="E8">
-        <v>-640.9599999999999</v>
+        <v>-624.8199999999999</v>
       </c>
       <c r="F8">
-        <v>96.84</v>
+        <v>112.98</v>
       </c>
       <c r="G8">
         <v>308.9</v>
@@ -1949,28 +1949,28 @@
         <v>117.45</v>
       </c>
       <c r="M8">
-        <v>4.871052</v>
+        <v>5.682893999999999</v>
       </c>
       <c r="N8">
-        <v>112.578948</v>
+        <v>111.767106</v>
       </c>
       <c r="O8">
-        <v>27.01894751999999</v>
+        <v>26.82410544</v>
       </c>
       <c r="P8">
-        <v>85.56000047999999</v>
+        <v>84.94300055999999</v>
       </c>
       <c r="Q8">
-        <v>183.36000048</v>
+        <v>182.74300056</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09599028303020643</v>
+        <v>0.09640643273763813</v>
       </c>
       <c r="T8">
-        <v>1.031965045289229</v>
+        <v>1.040521521279182</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.11183456879541</v>
+        <v>20.66728677325321</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09233394244600346</v>
+        <v>0.09214333884361289</v>
       </c>
       <c r="C9">
-        <v>1405.714788426852</v>
+        <v>1394.550503396496</v>
       </c>
       <c r="D9">
-        <v>1209.794788426851</v>
+        <v>1214.770503396496</v>
       </c>
       <c r="E9">
-        <v>-624.8199999999999</v>
+        <v>-608.6799999999999</v>
       </c>
       <c r="F9">
-        <v>112.98</v>
+        <v>129.12</v>
       </c>
       <c r="G9">
         <v>308.9</v>
@@ -2031,28 +2031,28 @@
         <v>117.45</v>
       </c>
       <c r="M9">
-        <v>5.682894</v>
+        <v>6.494736</v>
       </c>
       <c r="N9">
-        <v>111.767106</v>
+        <v>110.955264</v>
       </c>
       <c r="O9">
-        <v>26.82410544</v>
+        <v>26.62926336</v>
       </c>
       <c r="P9">
-        <v>84.94300055999999</v>
+        <v>84.32600063999999</v>
       </c>
       <c r="Q9">
-        <v>182.74300056</v>
+        <v>182.12600064</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09640643273763813</v>
+        <v>0.09683162917784009</v>
       </c>
       <c r="T9">
-        <v>1.040521521279182</v>
+        <v>1.049264007616741</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.6672867732532</v>
+        <v>18.08387592659655</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09214333884361289</v>
+        <v>0.09195273524122233</v>
       </c>
       <c r="C10">
-        <v>1394.550503396496</v>
+        <v>1383.42731622059</v>
       </c>
       <c r="D10">
-        <v>1214.770503396496</v>
+        <v>1219.78731622059</v>
       </c>
       <c r="E10">
-        <v>-608.6799999999999</v>
+        <v>-592.54</v>
       </c>
       <c r="F10">
-        <v>129.12</v>
+        <v>145.26</v>
       </c>
       <c r="G10">
         <v>308.9</v>
@@ -2113,28 +2113,28 @@
         <v>117.45</v>
       </c>
       <c r="M10">
-        <v>6.494736</v>
+        <v>7.306577999999999</v>
       </c>
       <c r="N10">
-        <v>110.955264</v>
+        <v>110.143422</v>
       </c>
       <c r="O10">
-        <v>26.62926336</v>
+        <v>26.43442128</v>
       </c>
       <c r="P10">
-        <v>84.32600063999999</v>
+        <v>83.70900071999999</v>
       </c>
       <c r="Q10">
-        <v>182.12600064</v>
+        <v>181.50900072</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09683162917784009</v>
+        <v>0.0972661705947498</v>
       </c>
       <c r="T10">
-        <v>1.049264007616741</v>
+        <v>1.058198636511171</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.08387592659655</v>
+        <v>16.07455637919694</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09195273524122233</v>
+        <v>0.09176213163883176</v>
       </c>
       <c r="C11">
-        <v>1383.42731622059</v>
+        <v>1372.345738193899</v>
       </c>
       <c r="D11">
-        <v>1219.78731622059</v>
+        <v>1224.845738193899</v>
       </c>
       <c r="E11">
-        <v>-592.54</v>
+        <v>-576.4</v>
       </c>
       <c r="F11">
-        <v>145.26</v>
+        <v>161.4</v>
       </c>
       <c r="G11">
         <v>308.9</v>
@@ -2195,28 +2195,28 @@
         <v>117.45</v>
       </c>
       <c r="M11">
-        <v>7.306577999999999</v>
+        <v>8.118419999999999</v>
       </c>
       <c r="N11">
-        <v>110.143422</v>
+        <v>109.33158</v>
       </c>
       <c r="O11">
-        <v>26.43442128</v>
+        <v>26.2395792</v>
       </c>
       <c r="P11">
-        <v>83.70900071999999</v>
+        <v>83.09200079999999</v>
       </c>
       <c r="Q11">
-        <v>181.50900072</v>
+        <v>180.8920008</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0972661705947498</v>
+        <v>0.09771036848759085</v>
       </c>
       <c r="T11">
-        <v>1.058198636511171</v>
+        <v>1.067331812714365</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.07455637919694</v>
+        <v>14.46710074127724</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09176213163883176</v>
+        <v>0.09157152803644118</v>
       </c>
       <c r="C12">
-        <v>1372.345738193899</v>
+        <v>1361.306289127803</v>
       </c>
       <c r="D12">
-        <v>1224.845738193899</v>
+        <v>1229.946289127803</v>
       </c>
       <c r="E12">
-        <v>-576.4</v>
+        <v>-560.26</v>
       </c>
       <c r="F12">
-        <v>161.4</v>
+        <v>177.54</v>
       </c>
       <c r="G12">
         <v>308.9</v>
@@ -2277,28 +2277,28 @@
         <v>117.45</v>
       </c>
       <c r="M12">
-        <v>8.11842</v>
+        <v>8.930261999999999</v>
       </c>
       <c r="N12">
-        <v>109.33158</v>
+        <v>108.519738</v>
       </c>
       <c r="O12">
-        <v>26.2395792</v>
+        <v>26.04473712</v>
       </c>
       <c r="P12">
-        <v>83.09200079999999</v>
+        <v>82.47500088</v>
       </c>
       <c r="Q12">
-        <v>180.8920008</v>
+        <v>180.27500088</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09771036848759085</v>
+        <v>0.09816454835555188</v>
       </c>
       <c r="T12">
-        <v>1.067331812714365</v>
+        <v>1.076670228832238</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.46710074127724</v>
+        <v>13.15190976479749</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09157152803644118</v>
+        <v>0.09151772443405062</v>
       </c>
       <c r="C13">
-        <v>1361.306289127803</v>
+        <v>1346.613770206995</v>
       </c>
       <c r="D13">
-        <v>1229.946289127803</v>
+        <v>1231.393770206995</v>
       </c>
       <c r="E13">
-        <v>-560.26</v>
+        <v>-544.1199999999999</v>
       </c>
       <c r="F13">
-        <v>177.54</v>
+        <v>193.68</v>
       </c>
       <c r="G13">
         <v>308.9</v>
@@ -2359,45 +2359,45 @@
         <v>117.45</v>
       </c>
       <c r="M13">
-        <v>8.930261999999999</v>
+        <v>10.032624</v>
       </c>
       <c r="N13">
-        <v>108.519738</v>
+        <v>107.417376</v>
       </c>
       <c r="O13">
-        <v>26.04473712</v>
+        <v>25.78017024</v>
       </c>
       <c r="P13">
-        <v>82.47500088</v>
+        <v>81.63720576</v>
       </c>
       <c r="Q13">
-        <v>180.27500088</v>
+        <v>179.43720576</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09816454835555188</v>
+        <v>0.09862905049323933</v>
       </c>
       <c r="T13">
-        <v>1.076670228832238</v>
+        <v>1.086220881680063</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.15190976479749</v>
+        <v>11.70680771052518</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09151772443405062</v>
+        <v>0.09133852083166003</v>
       </c>
       <c r="C14">
-        <v>1346.613770206995</v>
+        <v>1335.319562199189</v>
       </c>
       <c r="D14">
-        <v>1231.393770206995</v>
+        <v>1236.239562199189</v>
       </c>
       <c r="E14">
-        <v>-544.1199999999999</v>
+        <v>-527.98</v>
       </c>
       <c r="F14">
-        <v>193.68</v>
+        <v>209.82</v>
       </c>
       <c r="G14">
         <v>308.9</v>
@@ -2441,28 +2441,28 @@
         <v>117.45</v>
       </c>
       <c r="M14">
-        <v>10.032624</v>
+        <v>10.868676</v>
       </c>
       <c r="N14">
-        <v>107.417376</v>
+        <v>106.581324</v>
       </c>
       <c r="O14">
-        <v>25.78017024</v>
+        <v>25.57951776</v>
       </c>
       <c r="P14">
-        <v>81.63720576</v>
+        <v>81.00180623999999</v>
       </c>
       <c r="Q14">
-        <v>179.43720576</v>
+        <v>178.80180624</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09862905049323933</v>
+        <v>0.09910423084098854</v>
       </c>
       <c r="T14">
-        <v>1.086220881680063</v>
+        <v>1.095991089765769</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.70680771052518</v>
+        <v>10.80628404048479</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09133852083166003</v>
+        <v>0.09115931722926947</v>
       </c>
       <c r="C15">
-        <v>1335.319562199189</v>
+        <v>1324.063643276601</v>
       </c>
       <c r="D15">
-        <v>1236.239562199189</v>
+        <v>1241.123643276601</v>
       </c>
       <c r="E15">
-        <v>-527.98</v>
+        <v>-511.8399999999999</v>
       </c>
       <c r="F15">
-        <v>209.82</v>
+        <v>225.96</v>
       </c>
       <c r="G15">
         <v>308.9</v>
@@ -2523,28 +2523,28 @@
         <v>117.45</v>
       </c>
       <c r="M15">
-        <v>10.868676</v>
+        <v>11.704728</v>
       </c>
       <c r="N15">
-        <v>106.581324</v>
+        <v>105.745272</v>
       </c>
       <c r="O15">
-        <v>25.57951776</v>
+        <v>25.37886528</v>
       </c>
       <c r="P15">
-        <v>81.00180623999999</v>
+        <v>80.36640671999999</v>
       </c>
       <c r="Q15">
-        <v>178.80180624</v>
+        <v>178.16640672</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09910423084098854</v>
+        <v>0.09959046189449938</v>
       </c>
       <c r="T15">
-        <v>1.095991089765769</v>
+        <v>1.105988511993002</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.80628404048479</v>
+        <v>10.03440660902158</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09115931722926947</v>
+        <v>0.09117391362687891</v>
       </c>
       <c r="C16">
-        <v>1324.063643276601</v>
+        <v>1307.524384479384</v>
       </c>
       <c r="D16">
-        <v>1241.123643276601</v>
+        <v>1240.724384479384</v>
       </c>
       <c r="E16">
-        <v>-511.8399999999999</v>
+        <v>-495.6999999999999</v>
       </c>
       <c r="F16">
-        <v>225.96</v>
+        <v>242.1</v>
       </c>
       <c r="G16">
         <v>308.9</v>
@@ -2605,45 +2605,45 @@
         <v>117.45</v>
       </c>
       <c r="M16">
-        <v>11.704728</v>
+        <v>12.95235</v>
       </c>
       <c r="N16">
-        <v>105.745272</v>
+        <v>104.49765</v>
       </c>
       <c r="O16">
-        <v>25.37886528</v>
+        <v>25.079436</v>
       </c>
       <c r="P16">
-        <v>80.36640671999999</v>
+        <v>79.41821399999999</v>
       </c>
       <c r="Q16">
-        <v>178.16640672</v>
+        <v>177.218214</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09959046189449938</v>
+        <v>0.1000881336786811</v>
       </c>
       <c r="T16">
-        <v>1.105988511993002</v>
+        <v>1.116221167684406</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.03440660902158</v>
+        <v>9.067852551853523</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09117391362687891</v>
+        <v>0.09100763002448832</v>
       </c>
       <c r="C17">
-        <v>1307.524384479384</v>
+        <v>1295.948041545974</v>
       </c>
       <c r="D17">
-        <v>1240.724384479384</v>
+        <v>1245.288041545974</v>
       </c>
       <c r="E17">
-        <v>-495.6999999999999</v>
+        <v>-479.5599999999999</v>
       </c>
       <c r="F17">
-        <v>242.1</v>
+        <v>258.24</v>
       </c>
       <c r="G17">
         <v>308.9</v>
@@ -2687,28 +2687,28 @@
         <v>117.45</v>
       </c>
       <c r="M17">
-        <v>12.95235</v>
+        <v>13.81584</v>
       </c>
       <c r="N17">
-        <v>104.49765</v>
+        <v>103.63416</v>
       </c>
       <c r="O17">
-        <v>25.079436</v>
+        <v>24.8721984</v>
       </c>
       <c r="P17">
-        <v>79.41821399999999</v>
+        <v>78.76196159999999</v>
       </c>
       <c r="Q17">
-        <v>177.218214</v>
+        <v>176.5619616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1000881336786811</v>
+        <v>0.1005976547910575</v>
       </c>
       <c r="T17">
-        <v>1.116221167684406</v>
+        <v>1.126697458035129</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.067852551853525</v>
+        <v>8.50111176736268</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09100763002448832</v>
+        <v>0.09084134642209778</v>
       </c>
       <c r="C18">
-        <v>1295.948041545974</v>
+        <v>1284.405394822708</v>
       </c>
       <c r="D18">
-        <v>1245.288041545974</v>
+        <v>1249.885394822708</v>
       </c>
       <c r="E18">
-        <v>-479.5599999999999</v>
+        <v>-463.42</v>
       </c>
       <c r="F18">
-        <v>258.24</v>
+        <v>274.38</v>
       </c>
       <c r="G18">
         <v>308.9</v>
@@ -2769,28 +2769,28 @@
         <v>117.45</v>
       </c>
       <c r="M18">
-        <v>13.81584</v>
+        <v>14.67933</v>
       </c>
       <c r="N18">
-        <v>103.63416</v>
+        <v>102.77067</v>
       </c>
       <c r="O18">
-        <v>24.8721984</v>
+        <v>24.6649608</v>
       </c>
       <c r="P18">
-        <v>78.76196159999999</v>
+        <v>78.10570919999999</v>
       </c>
       <c r="Q18">
-        <v>176.5619616</v>
+        <v>175.9057092</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1005976547910575</v>
+        <v>0.1011194535205997</v>
       </c>
       <c r="T18">
-        <v>1.126697458035129</v>
+        <v>1.137426189117195</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.50111176736268</v>
+        <v>8.001046369282522</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09084134642209778</v>
+        <v>0.09078450281970719</v>
       </c>
       <c r="C19">
-        <v>1284.405394822708</v>
+        <v>1269.844782922246</v>
       </c>
       <c r="D19">
-        <v>1249.885394822708</v>
+        <v>1251.464782922246</v>
       </c>
       <c r="E19">
-        <v>-463.42</v>
+        <v>-447.2799999999999</v>
       </c>
       <c r="F19">
-        <v>274.38</v>
+        <v>290.52</v>
       </c>
       <c r="G19">
         <v>308.9</v>
@@ -2851,45 +2851,45 @@
         <v>117.45</v>
       </c>
       <c r="M19">
-        <v>14.67933</v>
+        <v>15.775236</v>
       </c>
       <c r="N19">
-        <v>102.77067</v>
+        <v>101.674764</v>
       </c>
       <c r="O19">
-        <v>24.6649608</v>
+        <v>24.40194335999999</v>
       </c>
       <c r="P19">
-        <v>78.10570919999999</v>
+        <v>77.27282063999999</v>
       </c>
       <c r="Q19">
-        <v>175.9057092</v>
+        <v>175.07282064</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1011194535205997</v>
+        <v>0.1016539790484234</v>
       </c>
       <c r="T19">
-        <v>1.137426189117195</v>
+        <v>1.148416596567116</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.001046369282522</v>
+        <v>7.445213497915338</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09078450281970721</v>
+        <v>0.09062429921731663</v>
       </c>
       <c r="C20">
-        <v>1269.844782922246</v>
+        <v>1258.177561526482</v>
       </c>
       <c r="D20">
-        <v>1251.464782922246</v>
+        <v>1255.937561526482</v>
       </c>
       <c r="E20">
-        <v>-447.28</v>
+        <v>-431.1399999999999</v>
       </c>
       <c r="F20">
-        <v>290.52</v>
+        <v>306.66</v>
       </c>
       <c r="G20">
         <v>308.9</v>
@@ -2933,28 +2933,28 @@
         <v>117.45</v>
       </c>
       <c r="M20">
-        <v>15.775236</v>
+        <v>16.651638</v>
       </c>
       <c r="N20">
-        <v>101.674764</v>
+        <v>100.798362</v>
       </c>
       <c r="O20">
-        <v>24.40194335999999</v>
+        <v>24.19160687999999</v>
       </c>
       <c r="P20">
-        <v>77.27282063999999</v>
+        <v>76.60675511999999</v>
       </c>
       <c r="Q20">
-        <v>175.07282064</v>
+        <v>174.40675512</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1016539790484234</v>
+        <v>0.1022017027374279</v>
       </c>
       <c r="T20">
-        <v>1.148416596567116</v>
+        <v>1.15967837210222</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.445213497915339</v>
+        <v>7.053360155919794</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09062429921731663</v>
+        <v>0.09046409561492606</v>
       </c>
       <c r="C21">
-        <v>1258.177561526482</v>
+        <v>1246.542426540852</v>
       </c>
       <c r="D21">
-        <v>1255.937561526482</v>
+        <v>1260.442426540852</v>
       </c>
       <c r="E21">
-        <v>-431.1399999999999</v>
+        <v>-414.9999999999999</v>
       </c>
       <c r="F21">
-        <v>306.66</v>
+        <v>322.8</v>
       </c>
       <c r="G21">
         <v>308.9</v>
@@ -3015,28 +3015,28 @@
         <v>117.45</v>
       </c>
       <c r="M21">
-        <v>16.651638</v>
+        <v>17.52804</v>
       </c>
       <c r="N21">
-        <v>100.798362</v>
+        <v>99.92195999999998</v>
       </c>
       <c r="O21">
-        <v>24.19160687999999</v>
+        <v>23.9812704</v>
       </c>
       <c r="P21">
-        <v>76.60675511999999</v>
+        <v>75.94068959999998</v>
       </c>
       <c r="Q21">
-        <v>174.40675512</v>
+        <v>173.7406896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1022017027374279</v>
+        <v>0.1027631195186576</v>
       </c>
       <c r="T21">
-        <v>1.15967837210222</v>
+        <v>1.171221692025702</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.053360155919794</v>
+        <v>6.700692148123805</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09046409561492606</v>
+        <v>0.09030389201253548</v>
       </c>
       <c r="C22">
-        <v>1246.542426540852</v>
+        <v>1234.939724476073</v>
       </c>
       <c r="D22">
-        <v>1260.442426540852</v>
+        <v>1264.979724476073</v>
       </c>
       <c r="E22">
-        <v>-414.9999999999999</v>
+        <v>-398.8599999999999</v>
       </c>
       <c r="F22">
-        <v>322.8</v>
+        <v>338.9400000000001</v>
       </c>
       <c r="G22">
         <v>308.9</v>
@@ -3097,28 +3097,28 @@
         <v>117.45</v>
       </c>
       <c r="M22">
-        <v>17.52804</v>
+        <v>18.404442</v>
       </c>
       <c r="N22">
-        <v>99.92195999999998</v>
+        <v>99.04555799999999</v>
       </c>
       <c r="O22">
-        <v>23.9812704</v>
+        <v>23.77093392</v>
       </c>
       <c r="P22">
-        <v>75.94068959999998</v>
+        <v>75.27462408</v>
       </c>
       <c r="Q22">
-        <v>173.7406896</v>
+        <v>173.07462408</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1027631195186576</v>
+        <v>0.1033387493829563</v>
       </c>
       <c r="T22">
-        <v>1.171221692025702</v>
+        <v>1.183057247896614</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.700692148123805</v>
+        <v>6.381611569641718</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09030389201253548</v>
+        <v>0.09031088841014492</v>
       </c>
       <c r="C23">
-        <v>1234.939724476073</v>
+        <v>1218.600889956331</v>
       </c>
       <c r="D23">
-        <v>1264.979724476073</v>
+        <v>1264.780889956331</v>
       </c>
       <c r="E23">
-        <v>-398.86</v>
+        <v>-382.72</v>
       </c>
       <c r="F23">
-        <v>338.94</v>
+        <v>355.08</v>
       </c>
       <c r="G23">
         <v>308.9</v>
@@ -3179,45 +3179,45 @@
         <v>117.45</v>
       </c>
       <c r="M23">
-        <v>18.404442</v>
+        <v>19.635924</v>
       </c>
       <c r="N23">
-        <v>99.04555799999999</v>
+        <v>97.81407599999999</v>
       </c>
       <c r="O23">
-        <v>23.77093392</v>
+        <v>23.47537823999999</v>
       </c>
       <c r="P23">
-        <v>75.27462408</v>
+        <v>74.33869775999999</v>
       </c>
       <c r="Q23">
-        <v>173.07462408</v>
+        <v>172.13869776</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1033387493829563</v>
+        <v>0.1039291389873653</v>
       </c>
       <c r="T23">
-        <v>1.183057247896614</v>
+        <v>1.195196279559088</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.38161156964172</v>
+        <v>5.981383916539909</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09031088841014492</v>
+        <v>0.09015828480775435</v>
       </c>
       <c r="C24">
-        <v>1218.600889956331</v>
+        <v>1206.812052785971</v>
       </c>
       <c r="D24">
-        <v>1264.780889956331</v>
+        <v>1269.132052785971</v>
       </c>
       <c r="E24">
-        <v>-382.72</v>
+        <v>-366.5799999999999</v>
       </c>
       <c r="F24">
-        <v>355.08</v>
+        <v>371.22</v>
       </c>
       <c r="G24">
         <v>308.9</v>
@@ -3261,28 +3261,28 @@
         <v>117.45</v>
       </c>
       <c r="M24">
-        <v>19.635924</v>
+        <v>20.528466</v>
       </c>
       <c r="N24">
-        <v>97.81407599999999</v>
+        <v>96.92153399999998</v>
       </c>
       <c r="O24">
-        <v>23.47537823999999</v>
+        <v>23.26116815999999</v>
       </c>
       <c r="P24">
-        <v>74.33869775999999</v>
+        <v>73.66036583999998</v>
       </c>
       <c r="Q24">
-        <v>172.13869776</v>
+        <v>171.46036584</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1039291389873653</v>
+        <v>0.104534863386694</v>
       </c>
       <c r="T24">
-        <v>1.195196279559088</v>
+        <v>1.207650610745262</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.981383916539909</v>
+        <v>5.721323746255564</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09015828480775435</v>
+        <v>0.09000568120536379</v>
       </c>
       <c r="C25">
-        <v>1206.812052785971</v>
+        <v>1195.053257144405</v>
       </c>
       <c r="D25">
-        <v>1269.132052785971</v>
+        <v>1273.513257144405</v>
       </c>
       <c r="E25">
-        <v>-366.5799999999999</v>
+        <v>-350.4399999999999</v>
       </c>
       <c r="F25">
-        <v>371.22</v>
+        <v>387.36</v>
       </c>
       <c r="G25">
         <v>308.9</v>
@@ -3343,28 +3343,28 @@
         <v>117.45</v>
       </c>
       <c r="M25">
-        <v>20.528466</v>
+        <v>21.421008</v>
       </c>
       <c r="N25">
-        <v>96.92153399999998</v>
+        <v>96.02899199999999</v>
       </c>
       <c r="O25">
-        <v>23.26116815999999</v>
+        <v>23.04695808</v>
       </c>
       <c r="P25">
-        <v>73.66036583999998</v>
+        <v>72.98203391999999</v>
       </c>
       <c r="Q25">
-        <v>171.46036584</v>
+        <v>170.78203392</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.104534863386694</v>
+        <v>0.1051565279017944</v>
       </c>
       <c r="T25">
-        <v>1.207650610745262</v>
+        <v>1.220432687488967</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.721323746255564</v>
+        <v>5.48293525682825</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09000568120536379</v>
+        <v>0.08985307760297322</v>
       </c>
       <c r="C26">
-        <v>1195.053257144405</v>
+        <v>1183.324815230854</v>
       </c>
       <c r="D26">
-        <v>1273.513257144405</v>
+        <v>1277.924815230854</v>
       </c>
       <c r="E26">
-        <v>-350.4399999999999</v>
+        <v>-334.3</v>
       </c>
       <c r="F26">
-        <v>387.36</v>
+        <v>403.5</v>
       </c>
       <c r="G26">
         <v>308.9</v>
@@ -3425,28 +3425,28 @@
         <v>117.45</v>
       </c>
       <c r="M26">
-        <v>21.421008</v>
+        <v>22.31355</v>
       </c>
       <c r="N26">
-        <v>96.02899199999999</v>
+        <v>95.13645</v>
       </c>
       <c r="O26">
-        <v>23.04695808</v>
+        <v>22.832748</v>
       </c>
       <c r="P26">
-        <v>72.98203391999999</v>
+        <v>72.303702</v>
       </c>
       <c r="Q26">
-        <v>170.78203392</v>
+        <v>170.103702</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1051565279017944</v>
+        <v>0.1057947701372976</v>
       </c>
       <c r="T26">
-        <v>1.220432687488967</v>
+        <v>1.233555619612504</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.48293525682825</v>
+        <v>5.26361784655512</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08985307760297322</v>
+        <v>0.08970047400058263</v>
       </c>
       <c r="C27">
-        <v>1183.324815230854</v>
+        <v>1171.627043585518</v>
       </c>
       <c r="D27">
-        <v>1277.924815230854</v>
+        <v>1282.367043585518</v>
       </c>
       <c r="E27">
-        <v>-334.3</v>
+        <v>-318.16</v>
       </c>
       <c r="F27">
-        <v>403.5</v>
+        <v>419.64</v>
       </c>
       <c r="G27">
         <v>308.9</v>
@@ -3507,28 +3507,28 @@
         <v>117.45</v>
       </c>
       <c r="M27">
-        <v>22.31355</v>
+        <v>23.206092</v>
       </c>
       <c r="N27">
-        <v>95.13645</v>
+        <v>94.24390799999999</v>
       </c>
       <c r="O27">
-        <v>22.832748</v>
+        <v>22.61853792</v>
       </c>
       <c r="P27">
-        <v>72.303702</v>
+        <v>71.62537008</v>
       </c>
       <c r="Q27">
-        <v>170.103702</v>
+        <v>169.42537008</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1057947701372976</v>
+        <v>0.1064502621629495</v>
       </c>
       <c r="T27">
-        <v>1.233555619612504</v>
+        <v>1.247033225577218</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.26361784655512</v>
+        <v>5.061171006303</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08970047400058263</v>
+        <v>0.08954787039819206</v>
       </c>
       <c r="C28">
-        <v>1171.627043585518</v>
+        <v>1159.96026316528</v>
       </c>
       <c r="D28">
-        <v>1282.367043585518</v>
+        <v>1286.84026316528</v>
       </c>
       <c r="E28">
-        <v>-318.16</v>
+        <v>-302.0199999999999</v>
       </c>
       <c r="F28">
-        <v>419.64</v>
+        <v>435.78</v>
       </c>
       <c r="G28">
         <v>308.9</v>
@@ -3589,28 +3589,28 @@
         <v>117.45</v>
       </c>
       <c r="M28">
-        <v>23.206092</v>
+        <v>24.098634</v>
       </c>
       <c r="N28">
-        <v>94.24390799999999</v>
+        <v>93.35136599999998</v>
       </c>
       <c r="O28">
-        <v>22.61853792</v>
+        <v>22.40432784</v>
       </c>
       <c r="P28">
-        <v>71.62537008</v>
+        <v>70.94703815999999</v>
       </c>
       <c r="Q28">
-        <v>169.42537008</v>
+        <v>168.74703816</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1064502621629495</v>
+        <v>0.1071237128742357</v>
       </c>
       <c r="T28">
-        <v>1.247033225577218</v>
+        <v>1.260880081020417</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.061171006303</v>
+        <v>4.873720228291777</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08954787039819206</v>
+        <v>0.0893952667958015</v>
       </c>
       <c r="C29">
-        <v>1159.96026316528</v>
+        <v>1148.324799421018</v>
       </c>
       <c r="D29">
-        <v>1286.84026316528</v>
+        <v>1291.344799421018</v>
       </c>
       <c r="E29">
-        <v>-302.0199999999999</v>
+        <v>-285.8799999999999</v>
       </c>
       <c r="F29">
-        <v>435.78</v>
+        <v>451.92</v>
       </c>
       <c r="G29">
         <v>308.9</v>
@@ -3671,28 +3671,28 @@
         <v>117.45</v>
       </c>
       <c r="M29">
-        <v>24.098634</v>
+        <v>24.991176</v>
       </c>
       <c r="N29">
-        <v>93.35136599999998</v>
+        <v>92.45882399999999</v>
       </c>
       <c r="O29">
-        <v>22.40432784</v>
+        <v>22.19011776</v>
       </c>
       <c r="P29">
-        <v>70.94703815999999</v>
+        <v>70.26870624</v>
       </c>
       <c r="Q29">
-        <v>168.74703816</v>
+        <v>168.06870624</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1071237128742357</v>
+        <v>0.1078158705497243</v>
       </c>
       <c r="T29">
-        <v>1.260880081020417</v>
+        <v>1.275111571337039</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.873720228291777</v>
+        <v>4.699658791567071</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0893952667958015</v>
+        <v>0.08924266319341093</v>
       </c>
       <c r="C30">
-        <v>1148.324799421018</v>
+        <v>1136.720982376529</v>
       </c>
       <c r="D30">
-        <v>1291.344799421018</v>
+        <v>1295.880982376529</v>
       </c>
       <c r="E30">
-        <v>-285.8799999999999</v>
+        <v>-269.7399999999999</v>
       </c>
       <c r="F30">
-        <v>451.92</v>
+        <v>468.0600000000001</v>
       </c>
       <c r="G30">
         <v>308.9</v>
@@ -3753,28 +3753,28 @@
         <v>117.45</v>
       </c>
       <c r="M30">
-        <v>24.991176</v>
+        <v>25.88371800000001</v>
       </c>
       <c r="N30">
-        <v>92.45882399999999</v>
+        <v>91.56628199999999</v>
       </c>
       <c r="O30">
-        <v>22.19011776</v>
+        <v>21.97590768</v>
       </c>
       <c r="P30">
-        <v>70.26870624</v>
+        <v>69.59037432</v>
       </c>
       <c r="Q30">
-        <v>168.06870624</v>
+        <v>167.39037432</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1078158705497243</v>
+        <v>0.1085275256245224</v>
       </c>
       <c r="T30">
-        <v>1.275111571337039</v>
+        <v>1.289743948704833</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.699658791567071</v>
+        <v>4.537601591857861</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08924266319341093</v>
+        <v>0.08966005959102036</v>
       </c>
       <c r="C31">
-        <v>1136.720982376529</v>
+        <v>1108.248667764597</v>
       </c>
       <c r="D31">
-        <v>1295.880982376529</v>
+        <v>1283.548667764597</v>
       </c>
       <c r="E31">
-        <v>-269.74</v>
+        <v>-253.6</v>
       </c>
       <c r="F31">
-        <v>468.0599999999999</v>
+        <v>484.2</v>
       </c>
       <c r="G31">
         <v>308.9</v>
@@ -3835,45 +3835,45 @@
         <v>117.45</v>
       </c>
       <c r="M31">
-        <v>25.883718</v>
+        <v>27.98676</v>
       </c>
       <c r="N31">
-        <v>91.56628199999999</v>
+        <v>89.46323999999998</v>
       </c>
       <c r="O31">
-        <v>21.97590768</v>
+        <v>21.4711776</v>
       </c>
       <c r="P31">
-        <v>69.59037432</v>
+        <v>67.99206239999998</v>
       </c>
       <c r="Q31">
-        <v>167.39037432</v>
+        <v>165.7920624</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1085275256245224</v>
+        <v>0.1092595137014576</v>
       </c>
       <c r="T31">
-        <v>1.289743948704833</v>
+        <v>1.304794393997421</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.537601591857862</v>
+        <v>4.196627262319753</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08966005959102036</v>
+        <v>0.08952645598862977</v>
       </c>
       <c r="C32">
-        <v>1108.248667764597</v>
+        <v>1096.030474871526</v>
       </c>
       <c r="D32">
-        <v>1283.548667764597</v>
+        <v>1287.470474871526</v>
       </c>
       <c r="E32">
-        <v>-253.6</v>
+        <v>-237.46</v>
       </c>
       <c r="F32">
-        <v>484.2</v>
+        <v>500.34</v>
       </c>
       <c r="G32">
         <v>308.9</v>
@@ -3917,28 +3917,28 @@
         <v>117.45</v>
       </c>
       <c r="M32">
-        <v>27.98676</v>
+        <v>28.919652</v>
       </c>
       <c r="N32">
-        <v>89.46323999999998</v>
+        <v>88.53034799999999</v>
       </c>
       <c r="O32">
-        <v>21.4711776</v>
+        <v>21.24728352</v>
       </c>
       <c r="P32">
-        <v>67.99206239999998</v>
+        <v>67.28306447999999</v>
       </c>
       <c r="Q32">
-        <v>165.7920624</v>
+        <v>165.08306448</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1092595137014576</v>
+        <v>0.1100127188241011</v>
       </c>
       <c r="T32">
-        <v>1.304794393997421</v>
+        <v>1.320281084081098</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.196627262319753</v>
+        <v>4.061252189341698</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08952645598862977</v>
+        <v>0.09024405238623921</v>
       </c>
       <c r="C33">
-        <v>1096.030474871526</v>
+        <v>1059.102897564953</v>
       </c>
       <c r="D33">
-        <v>1287.470474871526</v>
+        <v>1266.682897564953</v>
       </c>
       <c r="E33">
-        <v>-237.46</v>
+        <v>-221.3199999999999</v>
       </c>
       <c r="F33">
-        <v>500.34</v>
+        <v>516.48</v>
       </c>
       <c r="G33">
         <v>308.9</v>
@@ -3999,45 +3999,45 @@
         <v>117.45</v>
       </c>
       <c r="M33">
-        <v>28.919652</v>
+        <v>31.660224</v>
       </c>
       <c r="N33">
-        <v>88.53034799999999</v>
+        <v>85.78977599999999</v>
       </c>
       <c r="O33">
-        <v>21.24728352</v>
+        <v>20.58954624</v>
       </c>
       <c r="P33">
-        <v>67.28306447999999</v>
+        <v>65.20022975999998</v>
       </c>
       <c r="Q33">
-        <v>165.08306448</v>
+        <v>163.00022976</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1100127188241011</v>
+        <v>0.1107880770385871</v>
       </c>
       <c r="T33">
-        <v>1.320281084081098</v>
+        <v>1.33622326504959</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.061252189341698</v>
+        <v>3.709702117079146</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09024405238623921</v>
+        <v>0.09013704878384865</v>
       </c>
       <c r="C34">
-        <v>1059.102897564953</v>
+        <v>1046.0199263218</v>
       </c>
       <c r="D34">
-        <v>1266.682897564953</v>
+        <v>1269.7399263218</v>
       </c>
       <c r="E34">
-        <v>-221.3199999999999</v>
+        <v>-205.1799999999999</v>
       </c>
       <c r="F34">
-        <v>516.48</v>
+        <v>532.62</v>
       </c>
       <c r="G34">
         <v>308.9</v>
@@ -4081,28 +4081,28 @@
         <v>117.45</v>
       </c>
       <c r="M34">
-        <v>31.660224</v>
+        <v>32.649606</v>
       </c>
       <c r="N34">
-        <v>85.78977599999999</v>
+        <v>84.80039399999998</v>
       </c>
       <c r="O34">
-        <v>20.58954624</v>
+        <v>20.35209455999999</v>
       </c>
       <c r="P34">
-        <v>65.20022975999998</v>
+        <v>64.44829943999999</v>
       </c>
       <c r="Q34">
-        <v>163.00022976</v>
+        <v>162.24829944</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1107880770385871</v>
+        <v>0.111586580274401</v>
       </c>
       <c r="T34">
-        <v>1.33622326504959</v>
+        <v>1.352641332017141</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.709702117079146</v>
+        <v>3.597286901410081</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09013704878384865</v>
+        <v>0.09075356518145807</v>
       </c>
       <c r="C35">
-        <v>1046.0199263218</v>
+        <v>1012.466057541496</v>
       </c>
       <c r="D35">
-        <v>1269.7399263218</v>
+        <v>1252.326057541496</v>
       </c>
       <c r="E35">
-        <v>-205.1799999999999</v>
+        <v>-189.04</v>
       </c>
       <c r="F35">
-        <v>532.62</v>
+        <v>548.76</v>
       </c>
       <c r="G35">
         <v>308.9</v>
@@ -4163,45 +4163,45 @@
         <v>117.45</v>
       </c>
       <c r="M35">
-        <v>32.649606</v>
+        <v>35.175516</v>
       </c>
       <c r="N35">
-        <v>84.80039399999998</v>
+        <v>82.27448399999999</v>
       </c>
       <c r="O35">
-        <v>20.35209455999999</v>
+        <v>19.74587615999999</v>
       </c>
       <c r="P35">
-        <v>64.44829943999999</v>
+        <v>62.52860783999999</v>
       </c>
       <c r="Q35">
-        <v>162.24829944</v>
+        <v>160.32860784</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.111586580274401</v>
+        <v>0.1124092805779668</v>
       </c>
       <c r="T35">
-        <v>1.352641332017141</v>
+        <v>1.369556916165527</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.597286901410081</v>
+        <v>3.338970208709944</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09075356518145807</v>
+        <v>0.09066784157906749</v>
       </c>
       <c r="C36">
-        <v>1012.466057541496</v>
+        <v>998.7187267059098</v>
       </c>
       <c r="D36">
-        <v>1252.326057541496</v>
+        <v>1254.71872670591</v>
       </c>
       <c r="E36">
-        <v>-189.04</v>
+        <v>-172.8999999999999</v>
       </c>
       <c r="F36">
-        <v>548.76</v>
+        <v>564.9000000000001</v>
       </c>
       <c r="G36">
         <v>308.9</v>
@@ -4245,28 +4245,28 @@
         <v>117.45</v>
       </c>
       <c r="M36">
-        <v>35.175516</v>
+        <v>36.21009000000001</v>
       </c>
       <c r="N36">
-        <v>82.27448399999999</v>
+        <v>81.23990999999998</v>
       </c>
       <c r="O36">
-        <v>19.74587615999999</v>
+        <v>19.49757839999999</v>
       </c>
       <c r="P36">
-        <v>62.52860783999999</v>
+        <v>61.74233159999999</v>
       </c>
       <c r="Q36">
-        <v>160.32860784</v>
+        <v>159.5423316</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1124092805779668</v>
+        <v>0.1132572947370269</v>
       </c>
       <c r="T36">
-        <v>1.369556916165527</v>
+        <v>1.386992979826171</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.338970208709944</v>
+        <v>3.24357105988966</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09066784157906749</v>
+        <v>0.09058211797667694</v>
       </c>
       <c r="C37">
-        <v>998.7187267059098</v>
+        <v>984.9805561436364</v>
       </c>
       <c r="D37">
-        <v>1254.71872670591</v>
+        <v>1257.120556143636</v>
       </c>
       <c r="E37">
-        <v>-172.8999999999999</v>
+        <v>-156.7599999999999</v>
       </c>
       <c r="F37">
-        <v>564.9000000000001</v>
+        <v>581.0400000000001</v>
       </c>
       <c r="G37">
         <v>308.9</v>
@@ -4327,28 +4327,28 @@
         <v>117.45</v>
       </c>
       <c r="M37">
-        <v>36.21009000000001</v>
+        <v>37.24466400000001</v>
       </c>
       <c r="N37">
-        <v>81.23990999999998</v>
+        <v>80.20533599999999</v>
       </c>
       <c r="O37">
-        <v>19.49757839999999</v>
+        <v>19.24928063999999</v>
       </c>
       <c r="P37">
-        <v>61.74233159999999</v>
+        <v>60.95605535999999</v>
       </c>
       <c r="Q37">
-        <v>159.5423316</v>
+        <v>158.75605536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1132572947370269</v>
+        <v>0.1141318093385577</v>
       </c>
       <c r="T37">
-        <v>1.386992979826171</v>
+        <v>1.40497392047621</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.24357105988966</v>
+        <v>3.153471863781614</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09058211797667694</v>
+        <v>0.09049639437428636</v>
       </c>
       <c r="C38">
-        <v>984.9805561436365</v>
+        <v>971.2515985603794</v>
       </c>
       <c r="D38">
-        <v>1257.120556143636</v>
+        <v>1259.531598560379</v>
       </c>
       <c r="E38">
-        <v>-156.76</v>
+        <v>-140.62</v>
       </c>
       <c r="F38">
-        <v>581.04</v>
+        <v>597.1799999999999</v>
       </c>
       <c r="G38">
         <v>308.9</v>
@@ -4409,28 +4409,28 @@
         <v>117.45</v>
       </c>
       <c r="M38">
-        <v>37.244664</v>
+        <v>38.279238</v>
       </c>
       <c r="N38">
-        <v>80.20533599999999</v>
+        <v>79.170762</v>
       </c>
       <c r="O38">
-        <v>19.24928063999999</v>
+        <v>19.00098288</v>
       </c>
       <c r="P38">
-        <v>60.95605535999999</v>
+        <v>60.16977912</v>
       </c>
       <c r="Q38">
-        <v>158.75605536</v>
+        <v>157.96977912</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1141318093385577</v>
+        <v>0.115034086308391</v>
       </c>
       <c r="T38">
-        <v>1.40497392047621</v>
+        <v>1.423525684638949</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.153471863781614</v>
+        <v>3.068242894490219</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09049639437428636</v>
+        <v>0.0926633107718958</v>
       </c>
       <c r="C39">
-        <v>971.2515985603794</v>
+        <v>896.872015627103</v>
       </c>
       <c r="D39">
-        <v>1259.531598560379</v>
+        <v>1201.292015627103</v>
       </c>
       <c r="E39">
-        <v>-140.62</v>
+        <v>-124.4799999999999</v>
       </c>
       <c r="F39">
-        <v>597.1799999999999</v>
+        <v>613.3200000000001</v>
       </c>
       <c r="G39">
         <v>308.9</v>
@@ -4491,45 +4491,45 @@
         <v>117.45</v>
       </c>
       <c r="M39">
-        <v>38.279238</v>
+        <v>44.097708</v>
       </c>
       <c r="N39">
-        <v>79.170762</v>
+        <v>73.35229199999998</v>
       </c>
       <c r="O39">
-        <v>19.00098288</v>
+        <v>17.60455007999999</v>
       </c>
       <c r="P39">
-        <v>60.16977912</v>
+        <v>55.74774191999998</v>
       </c>
       <c r="Q39">
-        <v>157.96977912</v>
+        <v>153.54774192</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.115034086308391</v>
+        <v>0.1159654689869287</v>
       </c>
       <c r="T39">
-        <v>1.423525684638949</v>
+        <v>1.442675892806937</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.068242894490219</v>
+        <v>2.663403730642871</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0926633107718958</v>
+        <v>0.09263686716950523</v>
       </c>
       <c r="C40">
-        <v>896.872015627103</v>
+        <v>881.410252459239</v>
       </c>
       <c r="D40">
-        <v>1201.292015627103</v>
+        <v>1201.970252459239</v>
       </c>
       <c r="E40">
-        <v>-124.4799999999999</v>
+        <v>-108.3399999999999</v>
       </c>
       <c r="F40">
-        <v>613.3200000000001</v>
+        <v>629.46</v>
       </c>
       <c r="G40">
         <v>308.9</v>
@@ -4573,28 +4573,28 @@
         <v>117.45</v>
       </c>
       <c r="M40">
-        <v>44.097708</v>
+        <v>45.258174</v>
       </c>
       <c r="N40">
-        <v>73.35229199999998</v>
+        <v>72.19182599999999</v>
       </c>
       <c r="O40">
-        <v>17.60455007999999</v>
+        <v>17.32603824</v>
       </c>
       <c r="P40">
-        <v>55.74774191999998</v>
+        <v>54.86578775999999</v>
       </c>
       <c r="Q40">
-        <v>153.54774192</v>
+        <v>152.66578776</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1159654689869287</v>
+        <v>0.1169273888024676</v>
       </c>
       <c r="T40">
-        <v>1.442675892806937</v>
+        <v>1.462453976652564</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.663403730642871</v>
+        <v>2.595111327293054</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09263686716950523</v>
+        <v>0.09261042356711466</v>
       </c>
       <c r="C41">
-        <v>881.410252459239</v>
+        <v>865.9492555747682</v>
       </c>
       <c r="D41">
-        <v>1201.970252459239</v>
+        <v>1202.649255574768</v>
       </c>
       <c r="E41">
-        <v>-108.3399999999999</v>
+        <v>-92.19999999999993</v>
       </c>
       <c r="F41">
-        <v>629.46</v>
+        <v>645.6</v>
       </c>
       <c r="G41">
         <v>308.9</v>
@@ -4655,28 +4655,28 @@
         <v>117.45</v>
       </c>
       <c r="M41">
-        <v>45.258174</v>
+        <v>46.41864</v>
       </c>
       <c r="N41">
-        <v>72.19182599999999</v>
+        <v>71.03135999999998</v>
       </c>
       <c r="O41">
-        <v>17.32603824</v>
+        <v>17.0475264</v>
       </c>
       <c r="P41">
-        <v>54.86578775999999</v>
+        <v>53.98383359999998</v>
       </c>
       <c r="Q41">
-        <v>152.66578776</v>
+        <v>151.7838336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1169273888024676</v>
+        <v>0.1179213726118578</v>
       </c>
       <c r="T41">
-        <v>1.462453976652564</v>
+        <v>1.482891329959713</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.595111327293054</v>
+        <v>2.530233544110727</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09261042356711466</v>
+        <v>0.09379921996472408</v>
       </c>
       <c r="C42">
-        <v>865.9492555747682</v>
+        <v>820.0232485591198</v>
       </c>
       <c r="D42">
-        <v>1202.649255574768</v>
+        <v>1172.86324855912</v>
       </c>
       <c r="E42">
-        <v>-92.19999999999993</v>
+        <v>-76.05999999999995</v>
       </c>
       <c r="F42">
-        <v>645.6</v>
+        <v>661.74</v>
       </c>
       <c r="G42">
         <v>308.9</v>
@@ -4737,45 +4737,45 @@
         <v>117.45</v>
       </c>
       <c r="M42">
-        <v>46.41864</v>
+        <v>50.15989200000001</v>
       </c>
       <c r="N42">
-        <v>71.03135999999998</v>
+        <v>67.29010799999998</v>
       </c>
       <c r="O42">
-        <v>17.0475264</v>
+        <v>16.14962591999999</v>
       </c>
       <c r="P42">
-        <v>53.98383359999998</v>
+        <v>51.14048207999998</v>
       </c>
       <c r="Q42">
-        <v>151.7838336</v>
+        <v>148.94048208</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1179213726118578</v>
+        <v>0.1189490507876679</v>
       </c>
       <c r="T42">
-        <v>1.482891329959713</v>
+        <v>1.504021474904391</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.530233544110727</v>
+        <v>2.341512218566977</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09379921996472408</v>
+        <v>0.09380241636233352</v>
       </c>
       <c r="C43">
-        <v>820.0232485591198</v>
+        <v>803.8051496306075</v>
       </c>
       <c r="D43">
-        <v>1172.86324855912</v>
+        <v>1172.785149630608</v>
       </c>
       <c r="E43">
-        <v>-76.05999999999995</v>
+        <v>-59.91999999999985</v>
       </c>
       <c r="F43">
-        <v>661.74</v>
+        <v>677.8800000000001</v>
       </c>
       <c r="G43">
         <v>308.9</v>
@@ -4819,28 +4819,28 @@
         <v>117.45</v>
       </c>
       <c r="M43">
-        <v>50.15989200000001</v>
+        <v>51.38330400000001</v>
       </c>
       <c r="N43">
-        <v>67.29010799999998</v>
+        <v>66.06669599999998</v>
       </c>
       <c r="O43">
-        <v>16.14962591999999</v>
+        <v>15.85600703999999</v>
       </c>
       <c r="P43">
-        <v>51.14048207999998</v>
+        <v>50.21068895999998</v>
       </c>
       <c r="Q43">
-        <v>148.94048208</v>
+        <v>148.01068896</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1189490507876679</v>
+        <v>0.1200121661419543</v>
       </c>
       <c r="T43">
-        <v>1.504021474904391</v>
+        <v>1.525880245536817</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.341512218566977</v>
+        <v>2.285761927648716</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09380241636233352</v>
+        <v>0.09380561275994297</v>
       </c>
       <c r="C44">
-        <v>803.8051496306076</v>
+        <v>787.587061102347</v>
       </c>
       <c r="D44">
-        <v>1172.785149630608</v>
+        <v>1172.707061102347</v>
       </c>
       <c r="E44">
-        <v>-59.91999999999996</v>
+        <v>-43.77999999999997</v>
       </c>
       <c r="F44">
-        <v>677.88</v>
+        <v>694.02</v>
       </c>
       <c r="G44">
         <v>308.9</v>
@@ -4901,28 +4901,28 @@
         <v>117.45</v>
       </c>
       <c r="M44">
-        <v>51.383304</v>
+        <v>52.60671600000001</v>
       </c>
       <c r="N44">
-        <v>66.06669599999998</v>
+        <v>64.84328399999998</v>
       </c>
       <c r="O44">
-        <v>15.85600703999999</v>
+        <v>15.56238816</v>
       </c>
       <c r="P44">
-        <v>50.21068895999998</v>
+        <v>49.28089583999999</v>
       </c>
       <c r="Q44">
-        <v>148.01068896</v>
+        <v>147.08089584</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1200121661419543</v>
+        <v>0.1211125837893736</v>
       </c>
       <c r="T44">
-        <v>1.525880245536817</v>
+        <v>1.548505990577399</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.285761927648716</v>
+        <v>2.232604673517351</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09380561275994297</v>
+        <v>0.09380880915755238</v>
       </c>
       <c r="C45">
-        <v>787.587061102347</v>
+        <v>771.3689829722615</v>
       </c>
       <c r="D45">
-        <v>1172.707061102347</v>
+        <v>1172.628982972261</v>
       </c>
       <c r="E45">
-        <v>-43.77999999999997</v>
+        <v>-27.63999999999999</v>
       </c>
       <c r="F45">
-        <v>694.02</v>
+        <v>710.16</v>
       </c>
       <c r="G45">
         <v>308.9</v>
@@ -4983,28 +4983,28 @@
         <v>117.45</v>
       </c>
       <c r="M45">
-        <v>52.60671600000001</v>
+        <v>53.830128</v>
       </c>
       <c r="N45">
-        <v>64.84328399999998</v>
+        <v>63.61987199999999</v>
       </c>
       <c r="O45">
-        <v>15.56238816</v>
+        <v>15.26876928</v>
       </c>
       <c r="P45">
-        <v>49.28089583999999</v>
+        <v>48.35110271999999</v>
       </c>
       <c r="Q45">
-        <v>147.08089584</v>
+        <v>146.15110272</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1211125837893736</v>
+        <v>0.1222523020670578</v>
       </c>
       <c r="T45">
-        <v>1.548505990577399</v>
+        <v>1.571939797940858</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.232604673517351</v>
+        <v>2.181863658210138</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09380880915755238</v>
+        <v>0.09381200555516181</v>
       </c>
       <c r="C46">
-        <v>771.3689829722615</v>
+        <v>755.1509152382729</v>
       </c>
       <c r="D46">
-        <v>1172.628982972261</v>
+        <v>1172.550915238273</v>
       </c>
       <c r="E46">
-        <v>-27.63999999999999</v>
+        <v>-11.49999999999989</v>
       </c>
       <c r="F46">
-        <v>710.16</v>
+        <v>726.3000000000001</v>
       </c>
       <c r="G46">
         <v>308.9</v>
@@ -5065,28 +5065,28 @@
         <v>117.45</v>
       </c>
       <c r="M46">
-        <v>53.830128</v>
+        <v>55.05354000000001</v>
       </c>
       <c r="N46">
-        <v>63.61987199999999</v>
+        <v>62.39645999999998</v>
       </c>
       <c r="O46">
-        <v>15.26876928</v>
+        <v>14.97515039999999</v>
       </c>
       <c r="P46">
-        <v>48.35110271999999</v>
+        <v>47.42130959999999</v>
       </c>
       <c r="Q46">
-        <v>146.15110272</v>
+        <v>145.2213096</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1222523020670578</v>
+        <v>0.1234334646457487</v>
       </c>
       <c r="T46">
-        <v>1.571939797940858</v>
+        <v>1.596225743753898</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.181863658210138</v>
+        <v>2.133377799138801</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09381200555516181</v>
+        <v>0.09381520195277127</v>
       </c>
       <c r="C47">
-        <v>755.1509152382729</v>
+        <v>738.9328578983059</v>
       </c>
       <c r="D47">
-        <v>1172.550915238273</v>
+        <v>1172.472857898306</v>
       </c>
       <c r="E47">
-        <v>-11.49999999999989</v>
+        <v>4.6400000000001</v>
       </c>
       <c r="F47">
-        <v>726.3000000000001</v>
+        <v>742.4400000000001</v>
       </c>
       <c r="G47">
         <v>308.9</v>
@@ -5147,28 +5147,28 @@
         <v>117.45</v>
       </c>
       <c r="M47">
-        <v>55.05354000000001</v>
+        <v>56.27695200000001</v>
       </c>
       <c r="N47">
-        <v>62.39645999999998</v>
+        <v>61.17304799999998</v>
       </c>
       <c r="O47">
-        <v>14.97515039999999</v>
+        <v>14.68153151999999</v>
       </c>
       <c r="P47">
-        <v>47.42130959999999</v>
+        <v>46.49151647999999</v>
       </c>
       <c r="Q47">
-        <v>145.2213096</v>
+        <v>144.29151648</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1234334646457487</v>
+        <v>0.1246583739866134</v>
       </c>
       <c r="T47">
-        <v>1.596225743753898</v>
+        <v>1.621411169041495</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.133377799138801</v>
+        <v>2.087000020896653</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09381520195277127</v>
+        <v>0.09381839835038068</v>
       </c>
       <c r="C48">
-        <v>738.9328578983059</v>
+        <v>722.7148109502849</v>
       </c>
       <c r="D48">
-        <v>1172.472857898306</v>
+        <v>1172.394810950285</v>
       </c>
       <c r="E48">
-        <v>4.6400000000001</v>
+        <v>20.78000000000009</v>
       </c>
       <c r="F48">
-        <v>742.4400000000001</v>
+        <v>758.58</v>
       </c>
       <c r="G48">
         <v>308.9</v>
@@ -5229,28 +5229,28 @@
         <v>117.45</v>
       </c>
       <c r="M48">
-        <v>56.27695200000001</v>
+        <v>57.500364</v>
       </c>
       <c r="N48">
-        <v>61.17304799999998</v>
+        <v>59.94963599999998</v>
       </c>
       <c r="O48">
-        <v>14.68153151999999</v>
+        <v>14.38791264</v>
       </c>
       <c r="P48">
-        <v>46.49151647999999</v>
+        <v>45.56172335999999</v>
       </c>
       <c r="Q48">
-        <v>144.29151648</v>
+        <v>143.36172336</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1246583739866134</v>
+        <v>0.125929506321473</v>
       </c>
       <c r="T48">
-        <v>1.621411169041495</v>
+        <v>1.647546987736171</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.087000020896653</v>
+        <v>2.042595765132895</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09381839835038068</v>
+        <v>0.09382159474799009</v>
       </c>
       <c r="C49">
-        <v>722.7148109502849</v>
+        <v>706.496774392135</v>
       </c>
       <c r="D49">
-        <v>1172.394810950285</v>
+        <v>1172.316774392135</v>
       </c>
       <c r="E49">
-        <v>20.78000000000009</v>
+        <v>36.92000000000007</v>
       </c>
       <c r="F49">
-        <v>758.58</v>
+        <v>774.72</v>
       </c>
       <c r="G49">
         <v>308.9</v>
@@ -5311,28 +5311,28 @@
         <v>117.45</v>
       </c>
       <c r="M49">
-        <v>57.500364</v>
+        <v>58.72377600000001</v>
       </c>
       <c r="N49">
-        <v>59.94963599999998</v>
+        <v>58.72622399999998</v>
       </c>
       <c r="O49">
-        <v>14.38791264</v>
+        <v>14.09429375999999</v>
       </c>
       <c r="P49">
-        <v>45.56172335999999</v>
+        <v>44.63193023999999</v>
       </c>
       <c r="Q49">
-        <v>143.36172336</v>
+        <v>142.43193024</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.125929506321473</v>
+        <v>0.1272495283615194</v>
       </c>
       <c r="T49">
-        <v>1.647546987736171</v>
+        <v>1.674688030226796</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.042595765132895</v>
+        <v>2.000041686692626</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09382159474799009</v>
+        <v>0.09911287114559952</v>
       </c>
       <c r="C50">
-        <v>706.496774392135</v>
+        <v>574.0049076558277</v>
       </c>
       <c r="D50">
-        <v>1172.316774392135</v>
+        <v>1055.964907655828</v>
       </c>
       <c r="E50">
-        <v>36.92000000000007</v>
+        <v>53.06000000000006</v>
       </c>
       <c r="F50">
-        <v>774.72</v>
+        <v>790.86</v>
       </c>
       <c r="G50">
         <v>308.9</v>
@@ -5393,45 +5393,45 @@
         <v>117.45</v>
       </c>
       <c r="M50">
-        <v>58.72377600000001</v>
+        <v>71.17739999999999</v>
       </c>
       <c r="N50">
-        <v>58.72622399999998</v>
+        <v>46.2726</v>
       </c>
       <c r="O50">
-        <v>14.09429375999999</v>
+        <v>11.105424</v>
       </c>
       <c r="P50">
-        <v>44.63193023999999</v>
+        <v>35.167176</v>
       </c>
       <c r="Q50">
-        <v>142.43193024</v>
+        <v>132.967176</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1272495283615194</v>
+        <v>0.1286213159717638</v>
       </c>
       <c r="T50">
-        <v>1.674688030226796</v>
+        <v>1.702893427324896</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.000041686692626</v>
+        <v>1.650102420150216</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09911287114559952</v>
+        <v>0.09922398754320896</v>
       </c>
       <c r="C51">
-        <v>574.0049076558277</v>
+        <v>555.6686092899336</v>
       </c>
       <c r="D51">
-        <v>1055.964907655828</v>
+        <v>1053.768609289933</v>
       </c>
       <c r="E51">
-        <v>53.06000000000006</v>
+        <v>69.20000000000005</v>
       </c>
       <c r="F51">
-        <v>790.86</v>
+        <v>807</v>
       </c>
       <c r="G51">
         <v>308.9</v>
@@ -5475,28 +5475,28 @@
         <v>117.45</v>
       </c>
       <c r="M51">
-        <v>71.17739999999999</v>
+        <v>72.63</v>
       </c>
       <c r="N51">
-        <v>46.2726</v>
+        <v>44.81999999999999</v>
       </c>
       <c r="O51">
-        <v>11.105424</v>
+        <v>10.7568</v>
       </c>
       <c r="P51">
-        <v>35.167176</v>
+        <v>34.06319999999999</v>
       </c>
       <c r="Q51">
-        <v>132.967176</v>
+        <v>131.8632</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1286213159717638</v>
+        <v>0.1300479750864179</v>
       </c>
       <c r="T51">
-        <v>1.702893427324896</v>
+        <v>1.732227040306921</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.650102420150216</v>
+        <v>1.617100371747212</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09922398754320896</v>
+        <v>0.0993351039408184</v>
       </c>
       <c r="C52">
-        <v>555.6686092899336</v>
+        <v>537.3414281105032</v>
       </c>
       <c r="D52">
-        <v>1053.768609289933</v>
+        <v>1051.581428110503</v>
       </c>
       <c r="E52">
-        <v>69.20000000000005</v>
+        <v>85.34000000000003</v>
       </c>
       <c r="F52">
-        <v>807</v>
+        <v>823.14</v>
       </c>
       <c r="G52">
         <v>308.9</v>
@@ -5557,28 +5557,28 @@
         <v>117.45</v>
       </c>
       <c r="M52">
-        <v>72.63</v>
+        <v>74.0826</v>
       </c>
       <c r="N52">
-        <v>44.81999999999999</v>
+        <v>43.36739999999999</v>
       </c>
       <c r="O52">
-        <v>10.7568</v>
+        <v>10.408176</v>
       </c>
       <c r="P52">
-        <v>34.06319999999999</v>
+        <v>32.95922399999999</v>
       </c>
       <c r="Q52">
-        <v>131.8632</v>
+        <v>130.759224</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1300479750864179</v>
+        <v>0.1315328651853437</v>
       </c>
       <c r="T52">
-        <v>1.732227040306921</v>
+        <v>1.762757943614742</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.617100371747212</v>
+        <v>1.585392521320796</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0993351039408184</v>
+        <v>0.09944622033842783</v>
       </c>
       <c r="C53">
-        <v>537.3414281105032</v>
+        <v>519.0233074647711</v>
       </c>
       <c r="D53">
-        <v>1051.581428110503</v>
+        <v>1049.403307464771</v>
       </c>
       <c r="E53">
-        <v>85.34000000000003</v>
+        <v>101.48</v>
       </c>
       <c r="F53">
-        <v>823.14</v>
+        <v>839.28</v>
       </c>
       <c r="G53">
         <v>308.9</v>
@@ -5639,28 +5639,28 @@
         <v>117.45</v>
       </c>
       <c r="M53">
-        <v>74.0826</v>
+        <v>75.53519999999999</v>
       </c>
       <c r="N53">
-        <v>43.36739999999999</v>
+        <v>41.9148</v>
       </c>
       <c r="O53">
-        <v>10.408176</v>
+        <v>10.059552</v>
       </c>
       <c r="P53">
-        <v>32.95922399999999</v>
+        <v>31.855248</v>
       </c>
       <c r="Q53">
-        <v>130.759224</v>
+        <v>129.655248</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1315328651853437</v>
+        <v>0.133079625705058</v>
       </c>
       <c r="T53">
-        <v>1.762757943614742</v>
+        <v>1.794560967893723</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.585392521320796</v>
+        <v>1.554904203603088</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09944622033842783</v>
+        <v>0.09955733673603726</v>
       </c>
       <c r="C54">
-        <v>519.0233074647711</v>
+        <v>500.7141911683766</v>
       </c>
       <c r="D54">
-        <v>1049.403307464771</v>
+        <v>1047.234191168377</v>
       </c>
       <c r="E54">
-        <v>101.48</v>
+        <v>117.6200000000001</v>
       </c>
       <c r="F54">
-        <v>839.28</v>
+        <v>855.4200000000001</v>
       </c>
       <c r="G54">
         <v>308.9</v>
@@ -5721,28 +5721,28 @@
         <v>117.45</v>
       </c>
       <c r="M54">
-        <v>75.53519999999999</v>
+        <v>76.98780000000001</v>
       </c>
       <c r="N54">
-        <v>41.9148</v>
+        <v>40.46219999999998</v>
       </c>
       <c r="O54">
-        <v>10.059552</v>
+        <v>9.710927999999996</v>
       </c>
       <c r="P54">
-        <v>31.855248</v>
+        <v>30.75127199999999</v>
       </c>
       <c r="Q54">
-        <v>129.655248</v>
+        <v>128.551272</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.133079625705058</v>
+        <v>0.1346922058213559</v>
       </c>
       <c r="T54">
-        <v>1.794560967893723</v>
+        <v>1.827717312354788</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.554904203603088</v>
+        <v>1.525566388440766</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09955733673603726</v>
+        <v>0.1250486442568559</v>
       </c>
       <c r="C55">
-        <v>500.7141911683766</v>
+        <v>147.7183488543374</v>
       </c>
       <c r="D55">
-        <v>1047.234191168377</v>
+        <v>710.3783488543374</v>
       </c>
       <c r="E55">
-        <v>117.6200000000001</v>
+        <v>133.7600000000001</v>
       </c>
       <c r="F55">
-        <v>855.4200000000001</v>
+        <v>871.5600000000001</v>
       </c>
       <c r="G55">
         <v>308.9</v>
@@ -5803,45 +5803,45 @@
         <v>117.45</v>
       </c>
       <c r="M55">
-        <v>76.98780000000001</v>
+        <v>127.945008</v>
       </c>
       <c r="N55">
-        <v>40.46219999999998</v>
+        <v>-10.49500800000003</v>
       </c>
       <c r="O55">
-        <v>9.710927999999996</v>
+        <v>-2.518801920000006</v>
       </c>
       <c r="P55">
-        <v>30.75127199999999</v>
+        <v>-7.97620608000002</v>
       </c>
       <c r="Q55">
-        <v>128.551272</v>
+        <v>89.82379391999996</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1346922058213559</v>
+        <v>0.1374811484167951</v>
       </c>
       <c r="T55">
-        <v>1.827717312354788</v>
+        <v>1.88506090752996</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.24</v>
+        <v>0.2203134021453967</v>
       </c>
       <c r="W55">
-        <v>0.0684</v>
+        <v>0.1144579925650558</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.525566388440766</v>
+        <v>0.9179725089391528</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1250486442568559</v>
+        <v>0.1260586442568559</v>
       </c>
       <c r="C56">
-        <v>147.7183488543374</v>
+        <v>122.6387244813328</v>
       </c>
       <c r="D56">
-        <v>710.3783488543374</v>
+        <v>701.4387244813329</v>
       </c>
       <c r="E56">
-        <v>133.7600000000001</v>
+        <v>149.9000000000001</v>
       </c>
       <c r="F56">
-        <v>871.5600000000001</v>
+        <v>887.7</v>
       </c>
       <c r="G56">
         <v>308.9</v>
@@ -5885,37 +5885,37 @@
         <v>117.45</v>
       </c>
       <c r="M56">
-        <v>127.945008</v>
+        <v>130.31436</v>
       </c>
       <c r="N56">
-        <v>-10.49500800000003</v>
+        <v>-12.86436000000003</v>
       </c>
       <c r="O56">
-        <v>-2.518801920000006</v>
+        <v>-3.087446400000008</v>
       </c>
       <c r="P56">
-        <v>-7.97620608000002</v>
+        <v>-9.776913600000025</v>
       </c>
       <c r="Q56">
-        <v>89.82379391999996</v>
+        <v>88.02308639999995</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1374811484167951</v>
+        <v>0.1395185072705016</v>
       </c>
       <c r="T56">
-        <v>1.88506090752996</v>
+        <v>1.926951149919515</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2203134021453967</v>
+        <v>0.2163077039245712</v>
       </c>
       <c r="W56">
-        <v>0.1144579925650558</v>
+        <v>0.115046029063873</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9179725089391528</v>
+        <v>0.9012820996857136</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1260586442568559</v>
+        <v>0.1270686442568559</v>
       </c>
       <c r="C57">
-        <v>122.6387244813328</v>
+        <v>97.78130193535037</v>
       </c>
       <c r="D57">
-        <v>701.4387244813329</v>
+        <v>692.7213019353504</v>
       </c>
       <c r="E57">
-        <v>149.9000000000001</v>
+        <v>166.0400000000001</v>
       </c>
       <c r="F57">
-        <v>887.7</v>
+        <v>903.84</v>
       </c>
       <c r="G57">
         <v>308.9</v>
@@ -5967,37 +5967,37 @@
         <v>117.45</v>
       </c>
       <c r="M57">
-        <v>130.31436</v>
+        <v>132.683712</v>
       </c>
       <c r="N57">
-        <v>-12.86436000000003</v>
+        <v>-15.23371200000003</v>
       </c>
       <c r="O57">
-        <v>-3.087446400000008</v>
+        <v>-3.656090880000006</v>
       </c>
       <c r="P57">
-        <v>-9.776913600000025</v>
+        <v>-11.57762112000002</v>
       </c>
       <c r="Q57">
-        <v>88.02308639999995</v>
+        <v>86.22237887999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1395185072705016</v>
+        <v>0.1416484733448312</v>
       </c>
       <c r="T57">
-        <v>1.926951149919515</v>
+        <v>1.970745494235867</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2163077039245712</v>
+        <v>0.2124450663544896</v>
       </c>
       <c r="W57">
-        <v>0.115046029063873</v>
+        <v>0.1156130642591609</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9012820996857136</v>
+        <v>0.8851877764770402</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1270686442568559</v>
+        <v>0.1280786442568558</v>
       </c>
       <c r="C58">
-        <v>97.78130193535037</v>
+        <v>73.13789839395815</v>
       </c>
       <c r="D58">
-        <v>692.7213019353504</v>
+        <v>684.2178983939583</v>
       </c>
       <c r="E58">
-        <v>166.0400000000001</v>
+        <v>182.1800000000002</v>
       </c>
       <c r="F58">
-        <v>903.84</v>
+        <v>919.9800000000001</v>
       </c>
       <c r="G58">
         <v>308.9</v>
@@ -6049,37 +6049,37 @@
         <v>117.45</v>
       </c>
       <c r="M58">
-        <v>132.683712</v>
+        <v>135.053064</v>
       </c>
       <c r="N58">
-        <v>-15.23371200000003</v>
+        <v>-17.60306400000005</v>
       </c>
       <c r="O58">
-        <v>-3.656090880000006</v>
+        <v>-4.224735360000011</v>
       </c>
       <c r="P58">
-        <v>-11.57762112000002</v>
+        <v>-13.37832864000003</v>
       </c>
       <c r="Q58">
-        <v>86.22237887999997</v>
+        <v>84.42167135999995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1416484733448312</v>
+        <v>0.1438775076086645</v>
       </c>
       <c r="T58">
-        <v>1.970745494235867</v>
+        <v>2.016576784799492</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2124450663544896</v>
+        <v>0.2087179599272179</v>
       </c>
       <c r="W58">
-        <v>0.1156130642591609</v>
+        <v>0.1161602034826844</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8851877764770402</v>
+        <v>0.8696581663634078</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1280786442568558</v>
+        <v>0.1290886442568558</v>
       </c>
       <c r="C59">
-        <v>73.13789839395815</v>
+        <v>48.70072795080966</v>
       </c>
       <c r="D59">
-        <v>684.2178983939583</v>
+        <v>675.9207279508098</v>
       </c>
       <c r="E59">
-        <v>182.1800000000002</v>
+        <v>198.3200000000002</v>
       </c>
       <c r="F59">
-        <v>919.9800000000001</v>
+        <v>936.1200000000001</v>
       </c>
       <c r="G59">
         <v>308.9</v>
@@ -6131,37 +6131,37 @@
         <v>117.45</v>
       </c>
       <c r="M59">
-        <v>135.053064</v>
+        <v>137.422416</v>
       </c>
       <c r="N59">
-        <v>-17.60306400000005</v>
+        <v>-19.97241600000004</v>
       </c>
       <c r="O59">
-        <v>-4.224735360000011</v>
+        <v>-4.793379840000009</v>
       </c>
       <c r="P59">
-        <v>-13.37832864000003</v>
+        <v>-15.17903616000003</v>
       </c>
       <c r="Q59">
-        <v>84.42167135999995</v>
+        <v>82.62096383999996</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1438775076086645</v>
+        <v>0.1462126863612517</v>
       </c>
       <c r="T59">
-        <v>2.016576784799492</v>
+        <v>2.064590517770909</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2087179599272179</v>
+        <v>0.2051193744112314</v>
       </c>
       <c r="W59">
-        <v>0.1161602034826844</v>
+        <v>0.1166884758364312</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8696581663634078</v>
+        <v>0.8546640600467974</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1290886442568558</v>
+        <v>0.1300986442568558</v>
       </c>
       <c r="C60">
-        <v>48.70072795080989</v>
+        <v>24.46237783796334</v>
       </c>
       <c r="D60">
-        <v>675.9207279508098</v>
+        <v>667.8223778379634</v>
       </c>
       <c r="E60">
-        <v>198.3199999999999</v>
+        <v>214.46</v>
       </c>
       <c r="F60">
-        <v>936.1199999999999</v>
+        <v>952.26</v>
       </c>
       <c r="G60">
         <v>308.9</v>
@@ -6213,37 +6213,37 @@
         <v>117.45</v>
       </c>
       <c r="M60">
-        <v>137.422416</v>
+        <v>139.791768</v>
       </c>
       <c r="N60">
-        <v>-19.97241600000001</v>
+        <v>-22.34176800000003</v>
       </c>
       <c r="O60">
-        <v>-4.793379840000002</v>
+        <v>-5.362024320000007</v>
       </c>
       <c r="P60">
-        <v>-15.17903616000001</v>
+        <v>-16.97974368000002</v>
       </c>
       <c r="Q60">
-        <v>82.62096383999997</v>
+        <v>80.82025631999996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1462126863612517</v>
+        <v>0.1486617762725017</v>
       </c>
       <c r="T60">
-        <v>2.064590517770908</v>
+        <v>2.114946384058003</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2051193744112314</v>
+        <v>0.2016427748449393</v>
       </c>
       <c r="W60">
-        <v>0.1166884758364312</v>
+        <v>0.1171988406527629</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8546640600467975</v>
+        <v>0.8401782285205806</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1300986442568558</v>
+        <v>0.1311086442568559</v>
       </c>
       <c r="C61">
-        <v>24.46237783796334</v>
+        <v>0.4157863372766997</v>
       </c>
       <c r="D61">
-        <v>667.8223778379634</v>
+        <v>659.9157863372767</v>
       </c>
       <c r="E61">
-        <v>214.46</v>
+        <v>230.6</v>
       </c>
       <c r="F61">
-        <v>952.26</v>
+        <v>968.4</v>
       </c>
       <c r="G61">
         <v>308.9</v>
@@ -6295,37 +6295,37 @@
         <v>117.45</v>
       </c>
       <c r="M61">
-        <v>139.791768</v>
+        <v>142.16112</v>
       </c>
       <c r="N61">
-        <v>-22.34176800000003</v>
+        <v>-24.71112000000002</v>
       </c>
       <c r="O61">
-        <v>-5.362024320000007</v>
+        <v>-5.930668800000005</v>
       </c>
       <c r="P61">
-        <v>-16.97974368000002</v>
+        <v>-18.78045120000002</v>
       </c>
       <c r="Q61">
-        <v>80.82025631999996</v>
+        <v>79.01954879999997</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1486617762725017</v>
+        <v>0.1512333206793143</v>
       </c>
       <c r="T61">
-        <v>2.114946384058003</v>
+        <v>2.167820043659454</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2016427748449393</v>
+        <v>0.198282061930857</v>
       </c>
       <c r="W61">
-        <v>0.1171988406527629</v>
+        <v>0.1176921933085502</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8401782285205806</v>
+        <v>0.8261752580452375</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1311086442568559</v>
+        <v>0.1321186442568558</v>
       </c>
       <c r="C62">
-        <v>0.4157863372766997</v>
+        <v>-23.44577775746643</v>
       </c>
       <c r="D62">
-        <v>659.9157863372767</v>
+        <v>652.1942222425336</v>
       </c>
       <c r="E62">
-        <v>230.6</v>
+        <v>246.74</v>
       </c>
       <c r="F62">
-        <v>968.4</v>
+        <v>984.54</v>
       </c>
       <c r="G62">
         <v>308.9</v>
@@ -6377,37 +6377,37 @@
         <v>117.45</v>
       </c>
       <c r="M62">
-        <v>142.16112</v>
+        <v>144.530472</v>
       </c>
       <c r="N62">
-        <v>-24.71112000000002</v>
+        <v>-27.08047200000001</v>
       </c>
       <c r="O62">
-        <v>-5.930668800000005</v>
+        <v>-6.499313280000004</v>
       </c>
       <c r="P62">
-        <v>-18.78045120000002</v>
+        <v>-20.58115872000001</v>
       </c>
       <c r="Q62">
-        <v>79.01954879999997</v>
+        <v>77.21884127999996</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1512333206793143</v>
+        <v>0.1539367391582711</v>
       </c>
       <c r="T62">
-        <v>2.167820043659454</v>
+        <v>2.223405172984056</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.198282061930857</v>
+        <v>0.1950315363254331</v>
       </c>
       <c r="W62">
-        <v>0.1176921933085502</v>
+        <v>0.1181693704674264</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8261752580452375</v>
+        <v>0.8126314013559714</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1321186442568558</v>
+        <v>0.1681401249695781</v>
       </c>
       <c r="C63">
-        <v>-23.44577775746643</v>
+        <v>-231.6160017195576</v>
       </c>
       <c r="D63">
-        <v>652.1942222425336</v>
+        <v>460.1639982804423</v>
       </c>
       <c r="E63">
-        <v>246.74</v>
+        <v>262.88</v>
       </c>
       <c r="F63">
-        <v>984.54</v>
+        <v>1000.68</v>
       </c>
       <c r="G63">
         <v>308.9</v>
@@ -6459,45 +6459,45 @@
         <v>117.45</v>
       </c>
       <c r="M63">
-        <v>144.530472</v>
+        <v>200.936544</v>
       </c>
       <c r="N63">
-        <v>-27.08047200000001</v>
+        <v>-83.48654400000001</v>
       </c>
       <c r="O63">
-        <v>-6.499313280000004</v>
+        <v>-20.03677056</v>
       </c>
       <c r="P63">
-        <v>-20.58115872000001</v>
+        <v>-63.44977344000001</v>
       </c>
       <c r="Q63">
-        <v>77.21884127999996</v>
+        <v>34.35022655999997</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1539367391582711</v>
+        <v>0.1608126552222316</v>
       </c>
       <c r="T63">
-        <v>2.223405172984056</v>
+        <v>2.364781244286133</v>
       </c>
       <c r="U63">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1950315363254331</v>
+        <v>0.1402830935521614</v>
       </c>
       <c r="W63">
-        <v>0.1181693704674264</v>
+        <v>0.172631154814726</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8126314013559714</v>
+        <v>0.5845128898006726</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1681401249695781</v>
+        <v>0.1696901249695781</v>
       </c>
       <c r="C64">
-        <v>-231.6160017195576</v>
+        <v>-253.5131530462662</v>
       </c>
       <c r="D64">
-        <v>460.1639982804423</v>
+        <v>454.4068469537338</v>
       </c>
       <c r="E64">
-        <v>262.88</v>
+        <v>279.0200000000001</v>
       </c>
       <c r="F64">
-        <v>1000.68</v>
+        <v>1016.82</v>
       </c>
       <c r="G64">
         <v>308.9</v>
@@ -6541,37 +6541,37 @@
         <v>117.45</v>
       </c>
       <c r="M64">
-        <v>200.936544</v>
+        <v>204.177456</v>
       </c>
       <c r="N64">
-        <v>-83.48654400000001</v>
+        <v>-86.72745600000002</v>
       </c>
       <c r="O64">
-        <v>-20.03677056</v>
+        <v>-20.81458944</v>
       </c>
       <c r="P64">
-        <v>-63.44977344000001</v>
+        <v>-65.91286656000001</v>
       </c>
       <c r="Q64">
-        <v>34.35022655999997</v>
+        <v>31.88713343999997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1608126552222316</v>
+        <v>0.163921105363373</v>
       </c>
       <c r="T64">
-        <v>2.364781244286133</v>
+        <v>2.428694250888461</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1402830935521614</v>
+        <v>0.1380563777814922</v>
       </c>
       <c r="W64">
-        <v>0.172631154814726</v>
+        <v>0.1730782793414764</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5845128898006726</v>
+        <v>0.5752349074228841</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1696901249695781</v>
+        <v>0.1712401249695781</v>
       </c>
       <c r="C65">
-        <v>-253.5131530462662</v>
+        <v>-275.2680279752342</v>
       </c>
       <c r="D65">
-        <v>454.4068469537338</v>
+        <v>448.7919720247659</v>
       </c>
       <c r="E65">
-        <v>279.0200000000001</v>
+        <v>295.1600000000001</v>
       </c>
       <c r="F65">
-        <v>1016.82</v>
+        <v>1032.96</v>
       </c>
       <c r="G65">
         <v>308.9</v>
@@ -6623,37 +6623,37 @@
         <v>117.45</v>
       </c>
       <c r="M65">
-        <v>204.177456</v>
+        <v>207.418368</v>
       </c>
       <c r="N65">
-        <v>-86.72745600000002</v>
+        <v>-89.96836800000003</v>
       </c>
       <c r="O65">
-        <v>-20.81458944</v>
+        <v>-21.59240832</v>
       </c>
       <c r="P65">
-        <v>-65.91286656000001</v>
+        <v>-68.37595968000002</v>
       </c>
       <c r="Q65">
-        <v>31.88713343999997</v>
+        <v>29.42404031999996</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.163921105363373</v>
+        <v>0.1672022471790222</v>
       </c>
       <c r="T65">
-        <v>2.428694250888461</v>
+        <v>2.496157980079807</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1380563777814922</v>
+        <v>0.1358992468786563</v>
       </c>
       <c r="W65">
-        <v>0.1730782793414764</v>
+        <v>0.1735114312267658</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5752349074228841</v>
+        <v>0.5662468619944014</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1712401249695781</v>
+        <v>0.1727901249695781</v>
       </c>
       <c r="C66">
-        <v>-275.2680279752342</v>
+        <v>-296.885836244224</v>
       </c>
       <c r="D66">
-        <v>448.7919720247659</v>
+        <v>443.3141637557762</v>
       </c>
       <c r="E66">
-        <v>295.1600000000001</v>
+        <v>311.3000000000002</v>
       </c>
       <c r="F66">
-        <v>1032.96</v>
+        <v>1049.1</v>
       </c>
       <c r="G66">
         <v>308.9</v>
@@ -6705,37 +6705,37 @@
         <v>117.45</v>
       </c>
       <c r="M66">
-        <v>207.418368</v>
+        <v>210.65928</v>
       </c>
       <c r="N66">
-        <v>-89.96836800000003</v>
+        <v>-93.20928000000004</v>
       </c>
       <c r="O66">
-        <v>-21.59240832</v>
+        <v>-22.37022720000001</v>
       </c>
       <c r="P66">
-        <v>-68.37595968000002</v>
+        <v>-70.83905280000002</v>
       </c>
       <c r="Q66">
-        <v>29.42404031999996</v>
+        <v>26.96094719999996</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1672022471790222</v>
+        <v>0.1706708828127086</v>
       </c>
       <c r="T66">
-        <v>2.496157980079807</v>
+        <v>2.567476779510659</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1358992468786563</v>
+        <v>0.1338084892343693</v>
       </c>
       <c r="W66">
-        <v>0.1735114312267658</v>
+        <v>0.1739312553617386</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5662468619944014</v>
+        <v>0.5575353718098722</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1727901249695781</v>
+        <v>0.1743401249695781</v>
       </c>
       <c r="C67">
-        <v>-296.885836244224</v>
+        <v>-318.3715363046842</v>
       </c>
       <c r="D67">
-        <v>443.3141637557762</v>
+        <v>437.9684636953158</v>
       </c>
       <c r="E67">
-        <v>311.3000000000002</v>
+        <v>327.4400000000001</v>
       </c>
       <c r="F67">
-        <v>1049.1</v>
+        <v>1065.24</v>
       </c>
       <c r="G67">
         <v>308.9</v>
@@ -6787,37 +6787,37 @@
         <v>117.45</v>
       </c>
       <c r="M67">
-        <v>210.65928</v>
+        <v>213.900192</v>
       </c>
       <c r="N67">
-        <v>-93.20928000000004</v>
+        <v>-96.45019200000002</v>
       </c>
       <c r="O67">
-        <v>-22.37022720000001</v>
+        <v>-23.14804608</v>
       </c>
       <c r="P67">
-        <v>-70.83905280000002</v>
+        <v>-73.30214592000002</v>
       </c>
       <c r="Q67">
-        <v>26.96094719999996</v>
+        <v>24.49785407999997</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1706708828127086</v>
+        <v>0.1743435558366118</v>
       </c>
       <c r="T67">
-        <v>2.567476779510659</v>
+        <v>2.642990802437443</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1338084892343693</v>
+        <v>0.1317810878823334</v>
       </c>
       <c r="W67">
-        <v>0.1739312553617386</v>
+        <v>0.1743383575532274</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5575353718098722</v>
+        <v>0.5490878661763894</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1743401249695781</v>
+        <v>0.1758901249695781</v>
       </c>
       <c r="C68">
-        <v>-318.3715363046842</v>
+        <v>-339.7298502919027</v>
       </c>
       <c r="D68">
-        <v>437.9684636953158</v>
+        <v>432.7501497080974</v>
       </c>
       <c r="E68">
-        <v>327.4400000000001</v>
+        <v>343.5800000000002</v>
       </c>
       <c r="F68">
-        <v>1065.24</v>
+        <v>1081.38</v>
       </c>
       <c r="G68">
         <v>308.9</v>
@@ -6869,37 +6869,37 @@
         <v>117.45</v>
       </c>
       <c r="M68">
-        <v>213.900192</v>
+        <v>217.141104</v>
       </c>
       <c r="N68">
-        <v>-96.45019200000002</v>
+        <v>-99.69110400000005</v>
       </c>
       <c r="O68">
-        <v>-23.14804608</v>
+        <v>-23.92586496000001</v>
       </c>
       <c r="P68">
-        <v>-73.30214592000002</v>
+        <v>-75.76523904000004</v>
       </c>
       <c r="Q68">
-        <v>24.49785407999997</v>
+        <v>22.03476095999994</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1743435558366118</v>
+        <v>0.1782388151043879</v>
       </c>
       <c r="T68">
-        <v>2.642990802437443</v>
+        <v>2.723081432814336</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1317810878823334</v>
+        <v>0.1298142059736419</v>
       </c>
       <c r="W68">
-        <v>0.1743383575532274</v>
+        <v>0.1747333074404927</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5490878661763894</v>
+        <v>0.5408925248901745</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1758901249695781</v>
+        <v>0.1774401249695781</v>
       </c>
       <c r="C69">
-        <v>-339.7298502919027</v>
+        <v>-360.9652779375582</v>
       </c>
       <c r="D69">
-        <v>432.7501497080974</v>
+        <v>427.6547220624418</v>
       </c>
       <c r="E69">
-        <v>343.5800000000002</v>
+        <v>359.72</v>
       </c>
       <c r="F69">
-        <v>1081.38</v>
+        <v>1097.52</v>
       </c>
       <c r="G69">
         <v>308.9</v>
@@ -6951,37 +6951,37 @@
         <v>117.45</v>
       </c>
       <c r="M69">
-        <v>217.141104</v>
+        <v>220.382016</v>
       </c>
       <c r="N69">
-        <v>-99.69110400000005</v>
+        <v>-102.932016</v>
       </c>
       <c r="O69">
-        <v>-23.92586496000001</v>
+        <v>-24.70368384</v>
       </c>
       <c r="P69">
-        <v>-75.76523904000004</v>
+        <v>-78.22833216000001</v>
       </c>
       <c r="Q69">
-        <v>22.03476095999994</v>
+        <v>19.57166783999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1782388151043879</v>
+        <v>0.1823775280764</v>
       </c>
       <c r="T69">
-        <v>2.723081432814336</v>
+        <v>2.808177727589784</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1298142059736419</v>
+        <v>0.1279051735328531</v>
       </c>
       <c r="W69">
-        <v>0.1747333074404927</v>
+        <v>0.1751166411546031</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5408925248901745</v>
+        <v>0.5329382230535544</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1774401249695781</v>
+        <v>0.1789901249695781</v>
       </c>
       <c r="C70">
-        <v>-360.9652779375582</v>
+        <v>-382.0821095108314</v>
       </c>
       <c r="D70">
-        <v>427.6547220624418</v>
+        <v>422.6778904891687</v>
       </c>
       <c r="E70">
-        <v>359.72</v>
+        <v>375.8600000000001</v>
       </c>
       <c r="F70">
-        <v>1097.52</v>
+        <v>1113.66</v>
       </c>
       <c r="G70">
         <v>308.9</v>
@@ -7033,37 +7033,37 @@
         <v>117.45</v>
       </c>
       <c r="M70">
-        <v>220.382016</v>
+        <v>223.622928</v>
       </c>
       <c r="N70">
-        <v>-102.932016</v>
+        <v>-106.172928</v>
       </c>
       <c r="O70">
-        <v>-24.70368384</v>
+        <v>-25.48150272000001</v>
       </c>
       <c r="P70">
-        <v>-78.22833216000001</v>
+        <v>-80.69142528000003</v>
       </c>
       <c r="Q70">
-        <v>19.57166783999998</v>
+        <v>17.10857471999995</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1823775280764</v>
+        <v>0.186783254788542</v>
       </c>
       <c r="T70">
-        <v>2.808177727589784</v>
+        <v>2.898764105899132</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1279051735328531</v>
+        <v>0.1260514753657102</v>
       </c>
       <c r="W70">
-        <v>0.1751166411546031</v>
+        <v>0.1754888637465654</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5329382230535544</v>
+        <v>0.5252144806904593</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1789901249695781</v>
+        <v>0.1805401249695781</v>
       </c>
       <c r="C71">
-        <v>-382.0821095108314</v>
+        <v>-403.0844378662946</v>
       </c>
       <c r="D71">
-        <v>422.6778904891687</v>
+        <v>417.8155621337057</v>
       </c>
       <c r="E71">
-        <v>375.8600000000001</v>
+        <v>392.0000000000002</v>
       </c>
       <c r="F71">
-        <v>1113.66</v>
+        <v>1129.8</v>
       </c>
       <c r="G71">
         <v>308.9</v>
@@ -7115,37 +7115,37 @@
         <v>117.45</v>
       </c>
       <c r="M71">
-        <v>223.622928</v>
+        <v>226.86384</v>
       </c>
       <c r="N71">
-        <v>-106.172928</v>
+        <v>-109.4138400000001</v>
       </c>
       <c r="O71">
-        <v>-25.48150272000001</v>
+        <v>-26.25932160000001</v>
       </c>
       <c r="P71">
-        <v>-80.69142528000003</v>
+        <v>-83.15451840000004</v>
       </c>
       <c r="Q71">
-        <v>17.10857471999995</v>
+        <v>14.64548159999994</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.186783254788542</v>
+        <v>0.1914826966148267</v>
       </c>
       <c r="T71">
-        <v>2.898764105899132</v>
+        <v>2.99538957609577</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1260514753657102</v>
+        <v>0.1242507400033429</v>
       </c>
       <c r="W71">
-        <v>0.1754888637465654</v>
+        <v>0.1758504514073287</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5252144806904593</v>
+        <v>0.5177114166805956</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1805401249695781</v>
+        <v>0.1820901249695781</v>
       </c>
       <c r="C72">
-        <v>-403.0844378662946</v>
+        <v>-423.9761696696939</v>
       </c>
       <c r="D72">
-        <v>417.8155621337057</v>
+        <v>413.0638303303061</v>
       </c>
       <c r="E72">
-        <v>392.0000000000002</v>
+        <v>408.1400000000001</v>
       </c>
       <c r="F72">
-        <v>1129.8</v>
+        <v>1145.94</v>
       </c>
       <c r="G72">
         <v>308.9</v>
@@ -7197,37 +7197,37 @@
         <v>117.45</v>
       </c>
       <c r="M72">
-        <v>226.86384</v>
+        <v>230.104752</v>
       </c>
       <c r="N72">
-        <v>-109.4138400000001</v>
+        <v>-112.654752</v>
       </c>
       <c r="O72">
-        <v>-26.25932160000001</v>
+        <v>-27.03714048000001</v>
       </c>
       <c r="P72">
-        <v>-83.15451840000004</v>
+        <v>-85.61761152000003</v>
       </c>
       <c r="Q72">
-        <v>14.64548159999994</v>
+        <v>12.18238847999996</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1914826966148267</v>
+        <v>0.196506237877407</v>
       </c>
       <c r="T72">
-        <v>2.99538957609577</v>
+        <v>3.09867887182321</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1242507400033429</v>
+        <v>0.1225007295807607</v>
       </c>
       <c r="W72">
-        <v>0.1758504514073287</v>
+        <v>0.1762018535001833</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5177114166805956</v>
+        <v>0.5104197065865028</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1820901249695781</v>
+        <v>0.1836401249695781</v>
       </c>
       <c r="C73">
-        <v>-423.9761696696939</v>
+        <v>-444.761035866335</v>
       </c>
       <c r="D73">
-        <v>413.0638303303061</v>
+        <v>408.418964133665</v>
       </c>
       <c r="E73">
-        <v>408.1400000000001</v>
+        <v>424.28</v>
       </c>
       <c r="F73">
-        <v>1145.94</v>
+        <v>1162.08</v>
       </c>
       <c r="G73">
         <v>308.9</v>
@@ -7279,37 +7279,37 @@
         <v>117.45</v>
       </c>
       <c r="M73">
-        <v>230.104752</v>
+        <v>233.345664</v>
       </c>
       <c r="N73">
-        <v>-112.654752</v>
+        <v>-115.895664</v>
       </c>
       <c r="O73">
-        <v>-27.03714048000001</v>
+        <v>-27.81495936</v>
       </c>
       <c r="P73">
-        <v>-85.61761152000003</v>
+        <v>-88.08070464000001</v>
       </c>
       <c r="Q73">
-        <v>12.18238847999996</v>
+        <v>9.719295359999975</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1965062378774069</v>
+        <v>0.2018886035158857</v>
       </c>
       <c r="T73">
-        <v>3.098678871823209</v>
+        <v>3.209345974388323</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1225007295807607</v>
+        <v>0.1207993305588056</v>
       </c>
       <c r="W73">
-        <v>0.1762018535001833</v>
+        <v>0.1765434944237918</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5104197065865028</v>
+        <v>0.5033305439950235</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1836401249695781</v>
+        <v>0.2113580959353971</v>
       </c>
       <c r="C74">
-        <v>-444.761035866335</v>
+        <v>-529.2791174442013</v>
       </c>
       <c r="D74">
-        <v>408.418964133665</v>
+        <v>340.0408825557988</v>
       </c>
       <c r="E74">
-        <v>424.28</v>
+        <v>440.4200000000001</v>
       </c>
       <c r="F74">
-        <v>1162.08</v>
+        <v>1178.22</v>
       </c>
       <c r="G74">
         <v>308.9</v>
@@ -7361,45 +7361,45 @@
         <v>117.45</v>
       </c>
       <c r="M74">
-        <v>233.345664</v>
+        <v>277.824276</v>
       </c>
       <c r="N74">
-        <v>-115.895664</v>
+        <v>-160.374276</v>
       </c>
       <c r="O74">
-        <v>-27.81495936</v>
+        <v>-38.48982624</v>
       </c>
       <c r="P74">
-        <v>-88.08070464000001</v>
+        <v>-121.88444976</v>
       </c>
       <c r="Q74">
-        <v>9.719295359999975</v>
+        <v>-24.08444976000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2018886035158857</v>
+        <v>0.2099584442602483</v>
       </c>
       <c r="T74">
-        <v>3.209345974388323</v>
+        <v>3.375270393746967</v>
       </c>
       <c r="U74">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1207993305588056</v>
+        <v>0.1014598162760982</v>
       </c>
       <c r="W74">
-        <v>0.1765434944237918</v>
+        <v>0.211875775322096</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5033305439950235</v>
+        <v>0.4227492344837425</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2113580959353971</v>
+        <v>0.2132580959353972</v>
       </c>
       <c r="C75">
-        <v>-529.2791174442013</v>
+        <v>-549.2772628103427</v>
       </c>
       <c r="D75">
-        <v>340.0408825557988</v>
+        <v>336.1827371896572</v>
       </c>
       <c r="E75">
-        <v>440.4200000000001</v>
+        <v>456.5599999999999</v>
       </c>
       <c r="F75">
-        <v>1178.22</v>
+        <v>1194.36</v>
       </c>
       <c r="G75">
         <v>308.9</v>
@@ -7443,37 +7443,37 @@
         <v>117.45</v>
       </c>
       <c r="M75">
-        <v>277.824276</v>
+        <v>281.630088</v>
       </c>
       <c r="N75">
-        <v>-160.374276</v>
+        <v>-164.180088</v>
       </c>
       <c r="O75">
-        <v>-38.48982624</v>
+        <v>-39.40322112</v>
       </c>
       <c r="P75">
-        <v>-121.88444976</v>
+        <v>-124.77686688</v>
       </c>
       <c r="Q75">
-        <v>-24.08444976000003</v>
+        <v>-26.97686688000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2099584442602483</v>
+        <v>0.2162722305779501</v>
       </c>
       <c r="T75">
-        <v>3.375270393746967</v>
+        <v>3.505088485814158</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1014598162760982</v>
+        <v>0.1000887376777725</v>
       </c>
       <c r="W75">
-        <v>0.211875775322096</v>
+        <v>0.2121990756555812</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4227492344837425</v>
+        <v>0.417036406990719</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2132580959353972</v>
+        <v>0.2151580959353972</v>
       </c>
       <c r="C76">
-        <v>-549.2772628103427</v>
+        <v>-569.1888404082865</v>
       </c>
       <c r="D76">
-        <v>336.1827371896572</v>
+        <v>332.4111595917135</v>
       </c>
       <c r="E76">
-        <v>456.5599999999999</v>
+        <v>472.7</v>
       </c>
       <c r="F76">
-        <v>1194.36</v>
+        <v>1210.5</v>
       </c>
       <c r="G76">
         <v>308.9</v>
@@ -7525,37 +7525,37 @@
         <v>117.45</v>
       </c>
       <c r="M76">
-        <v>281.630088</v>
+        <v>285.4359</v>
       </c>
       <c r="N76">
-        <v>-164.180088</v>
+        <v>-167.9859</v>
       </c>
       <c r="O76">
-        <v>-39.40322112</v>
+        <v>-40.316616</v>
       </c>
       <c r="P76">
-        <v>-124.77686688</v>
+        <v>-127.669284</v>
       </c>
       <c r="Q76">
-        <v>-26.97686688000002</v>
+        <v>-29.86928400000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2162722305779501</v>
+        <v>0.2230911198010682</v>
       </c>
       <c r="T76">
-        <v>3.505088485814158</v>
+        <v>3.645292025246726</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1000887376777725</v>
+        <v>0.09875422117540224</v>
       </c>
       <c r="W76">
-        <v>0.2121990756555812</v>
+        <v>0.2125137546468402</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.417036406990719</v>
+        <v>0.411475921564176</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2151580959353972</v>
+        <v>0.2170580959353972</v>
       </c>
       <c r="C77">
-        <v>-569.1888404082865</v>
+        <v>-589.0167314815501</v>
       </c>
       <c r="D77">
-        <v>332.4111595917135</v>
+        <v>328.72326851845</v>
       </c>
       <c r="E77">
-        <v>472.7</v>
+        <v>488.8400000000001</v>
       </c>
       <c r="F77">
-        <v>1210.5</v>
+        <v>1226.64</v>
       </c>
       <c r="G77">
         <v>308.9</v>
@@ -7607,37 +7607,37 @@
         <v>117.45</v>
       </c>
       <c r="M77">
-        <v>285.4359</v>
+        <v>289.2417120000001</v>
       </c>
       <c r="N77">
-        <v>-167.9859</v>
+        <v>-171.7917120000001</v>
       </c>
       <c r="O77">
-        <v>-40.316616</v>
+        <v>-41.23001088000002</v>
       </c>
       <c r="P77">
-        <v>-127.669284</v>
+        <v>-130.5617011200001</v>
       </c>
       <c r="Q77">
-        <v>-29.86928400000002</v>
+        <v>-32.76170112000008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2230911198010682</v>
+        <v>0.2304782497927794</v>
       </c>
       <c r="T77">
-        <v>3.645292025246726</v>
+        <v>3.79717919296534</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09875422117540224</v>
+        <v>0.09745482352835745</v>
       </c>
       <c r="W77">
-        <v>0.2125137546468402</v>
+        <v>0.2128201526120133</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.411475921564176</v>
+        <v>0.4060617647014894</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2170580959353972</v>
+        <v>0.2189580959353972</v>
       </c>
       <c r="C78">
-        <v>-589.0167314815501</v>
+        <v>-608.7636908143558</v>
       </c>
       <c r="D78">
-        <v>328.72326851845</v>
+        <v>325.1163091856442</v>
       </c>
       <c r="E78">
-        <v>488.8400000000001</v>
+        <v>504.98</v>
       </c>
       <c r="F78">
-        <v>1226.64</v>
+        <v>1242.78</v>
       </c>
       <c r="G78">
         <v>308.9</v>
@@ -7689,37 +7689,37 @@
         <v>117.45</v>
       </c>
       <c r="M78">
-        <v>289.2417120000001</v>
+        <v>293.047524</v>
       </c>
       <c r="N78">
-        <v>-171.7917120000001</v>
+        <v>-175.597524</v>
       </c>
       <c r="O78">
-        <v>-41.23001088000002</v>
+        <v>-42.14340576</v>
       </c>
       <c r="P78">
-        <v>-130.5617011200001</v>
+        <v>-133.45411824</v>
       </c>
       <c r="Q78">
-        <v>-32.76170112000008</v>
+        <v>-35.65411824000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2304782497927794</v>
+        <v>0.2385077389142046</v>
       </c>
       <c r="T78">
-        <v>3.79717919296534</v>
+        <v>3.962273940485572</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09745482352835745</v>
+        <v>0.09618917646954762</v>
       </c>
       <c r="W78">
-        <v>0.2128201526120133</v>
+        <v>0.2131185921884807</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4060617647014894</v>
+        <v>0.4007882352897818</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2189580959353972</v>
+        <v>0.2208580959353972</v>
       </c>
       <c r="C79">
-        <v>-608.7636908143558</v>
+        <v>-628.4323535942863</v>
       </c>
       <c r="D79">
-        <v>325.1163091856442</v>
+        <v>321.5876464057138</v>
       </c>
       <c r="E79">
-        <v>504.98</v>
+        <v>521.1200000000001</v>
       </c>
       <c r="F79">
-        <v>1242.78</v>
+        <v>1258.92</v>
       </c>
       <c r="G79">
         <v>308.9</v>
@@ -7771,37 +7771,37 @@
         <v>117.45</v>
       </c>
       <c r="M79">
-        <v>293.047524</v>
+        <v>296.853336</v>
       </c>
       <c r="N79">
-        <v>-175.597524</v>
+        <v>-179.403336</v>
       </c>
       <c r="O79">
-        <v>-42.14340576</v>
+        <v>-43.05680064000001</v>
       </c>
       <c r="P79">
-        <v>-133.45411824</v>
+        <v>-136.34653536</v>
       </c>
       <c r="Q79">
-        <v>-35.65411824000003</v>
+        <v>-38.54653536000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2385077389142046</v>
+        <v>0.2472671815921229</v>
       </c>
       <c r="T79">
-        <v>3.962273940485572</v>
+        <v>4.142377301416734</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09618917646954762</v>
+        <v>0.09495598189942522</v>
       </c>
       <c r="W79">
-        <v>0.2131185921884807</v>
+        <v>0.2134093794681155</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4007882352897818</v>
+        <v>0.3956499245809385</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2208580959353972</v>
+        <v>0.2227580959353972</v>
       </c>
       <c r="C80">
-        <v>-628.4323535942863</v>
+        <v>-648.0252418328323</v>
       </c>
       <c r="D80">
-        <v>321.5876464057138</v>
+        <v>318.1347581671677</v>
       </c>
       <c r="E80">
-        <v>521.1200000000001</v>
+        <v>537.26</v>
       </c>
       <c r="F80">
-        <v>1258.92</v>
+        <v>1275.06</v>
       </c>
       <c r="G80">
         <v>308.9</v>
@@ -7853,37 +7853,37 @@
         <v>117.45</v>
       </c>
       <c r="M80">
-        <v>296.853336</v>
+        <v>300.659148</v>
       </c>
       <c r="N80">
-        <v>-179.403336</v>
+        <v>-183.209148</v>
       </c>
       <c r="O80">
-        <v>-43.05680064000001</v>
+        <v>-43.97019552</v>
       </c>
       <c r="P80">
-        <v>-136.34653536</v>
+        <v>-139.23895248</v>
       </c>
       <c r="Q80">
-        <v>-38.54653536000004</v>
+        <v>-41.43895248000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2472671815921229</v>
+        <v>0.2568608569060336</v>
       </c>
       <c r="T80">
-        <v>4.142377301416734</v>
+        <v>4.339633363388961</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09495598189942522</v>
+        <v>0.09375400744500212</v>
       </c>
       <c r="W80">
-        <v>0.2134093794681155</v>
+        <v>0.2136928050444685</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3956499245809385</v>
+        <v>0.3906416976875089</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2227580959353972</v>
+        <v>0.2246580959353972</v>
       </c>
       <c r="C81">
-        <v>-648.0252418328323</v>
+        <v>-667.544770376712</v>
       </c>
       <c r="D81">
-        <v>318.1347581671677</v>
+        <v>314.7552296232881</v>
       </c>
       <c r="E81">
-        <v>537.26</v>
+        <v>553.4000000000001</v>
       </c>
       <c r="F81">
-        <v>1275.06</v>
+        <v>1291.2</v>
       </c>
       <c r="G81">
         <v>308.9</v>
@@ -7935,37 +7935,37 @@
         <v>117.45</v>
       </c>
       <c r="M81">
-        <v>300.659148</v>
+        <v>304.46496</v>
       </c>
       <c r="N81">
-        <v>-183.209148</v>
+        <v>-187.01496</v>
       </c>
       <c r="O81">
-        <v>-43.97019552</v>
+        <v>-44.8835904</v>
       </c>
       <c r="P81">
-        <v>-139.23895248</v>
+        <v>-142.1313696</v>
       </c>
       <c r="Q81">
-        <v>-41.43895248000004</v>
+        <v>-44.33136960000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2568608569060336</v>
+        <v>0.2674138997513352</v>
       </c>
       <c r="T81">
-        <v>4.339633363388961</v>
+        <v>4.556615031558407</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09375400744500212</v>
+        <v>0.0925820823519396</v>
       </c>
       <c r="W81">
-        <v>0.2136928050444685</v>
+        <v>0.2139691449814126</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3906416976875089</v>
+        <v>0.385758676466415</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2246580959353972</v>
+        <v>0.2265580959353972</v>
       </c>
       <c r="C82">
-        <v>-667.544770376712</v>
+        <v>-686.9932525400669</v>
       </c>
       <c r="D82">
-        <v>314.7552296232881</v>
+        <v>311.4467474599332</v>
       </c>
       <c r="E82">
-        <v>553.4000000000001</v>
+        <v>569.5400000000002</v>
       </c>
       <c r="F82">
-        <v>1291.2</v>
+        <v>1307.34</v>
       </c>
       <c r="G82">
         <v>308.9</v>
@@ -8017,37 +8017,37 @@
         <v>117.45</v>
       </c>
       <c r="M82">
-        <v>304.46496</v>
+        <v>308.270772</v>
       </c>
       <c r="N82">
-        <v>-187.01496</v>
+        <v>-190.820772</v>
       </c>
       <c r="O82">
-        <v>-44.8835904</v>
+        <v>-45.79698528000001</v>
       </c>
       <c r="P82">
-        <v>-142.1313696</v>
+        <v>-145.02378672</v>
       </c>
       <c r="Q82">
-        <v>-44.33136960000004</v>
+        <v>-47.22378672000005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2674138997513352</v>
+        <v>0.2790777892119319</v>
       </c>
       <c r="T82">
-        <v>4.556615031558407</v>
+        <v>4.79643687532464</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0925820823519396</v>
+        <v>0.09143909368092799</v>
       </c>
       <c r="W82">
-        <v>0.2139691449814126</v>
+        <v>0.2142386617100372</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.385758676466415</v>
+        <v>0.3809962236705333</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2265580959353972</v>
+        <v>0.2284580959353972</v>
       </c>
       <c r="C83">
-        <v>-686.9932525400669</v>
+        <v>-706.3729053851459</v>
       </c>
       <c r="D83">
-        <v>311.4467474599332</v>
+        <v>308.207094614854</v>
       </c>
       <c r="E83">
-        <v>569.5400000000002</v>
+        <v>585.6800000000001</v>
       </c>
       <c r="F83">
-        <v>1307.34</v>
+        <v>1323.48</v>
       </c>
       <c r="G83">
         <v>308.9</v>
@@ -8099,37 +8099,37 @@
         <v>117.45</v>
       </c>
       <c r="M83">
-        <v>308.270772</v>
+        <v>312.076584</v>
       </c>
       <c r="N83">
-        <v>-190.820772</v>
+        <v>-194.626584</v>
       </c>
       <c r="O83">
-        <v>-45.79698528000001</v>
+        <v>-46.71038016000001</v>
       </c>
       <c r="P83">
-        <v>-145.02378672</v>
+        <v>-147.91620384</v>
       </c>
       <c r="Q83">
-        <v>-47.22378672000005</v>
+        <v>-50.11620384000005</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2790777892119319</v>
+        <v>0.2920376663903725</v>
       </c>
       <c r="T83">
-        <v>4.79643687532464</v>
+        <v>5.062905590620454</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09143909368092799</v>
+        <v>0.09032398278238009</v>
       </c>
       <c r="W83">
-        <v>0.2142386617100372</v>
+        <v>0.2145016048599148</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3809962236705333</v>
+        <v>0.3763499282599171</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2284580959353972</v>
+        <v>0.2303580959353972</v>
       </c>
       <c r="C84">
-        <v>-706.3729053851459</v>
+        <v>-725.6858546768055</v>
       </c>
       <c r="D84">
-        <v>308.207094614854</v>
+        <v>305.0341453231947</v>
       </c>
       <c r="E84">
-        <v>585.6800000000001</v>
+        <v>601.8200000000002</v>
       </c>
       <c r="F84">
-        <v>1323.48</v>
+        <v>1339.62</v>
       </c>
       <c r="G84">
         <v>308.9</v>
@@ -8181,37 +8181,37 @@
         <v>117.45</v>
       </c>
       <c r="M84">
-        <v>312.076584</v>
+        <v>315.882396</v>
       </c>
       <c r="N84">
-        <v>-194.626584</v>
+        <v>-198.432396</v>
       </c>
       <c r="O84">
-        <v>-46.71038016000001</v>
+        <v>-47.62377504000001</v>
       </c>
       <c r="P84">
-        <v>-147.91620384</v>
+        <v>-150.80862096</v>
       </c>
       <c r="Q84">
-        <v>-50.11620384000005</v>
+        <v>-53.00862096000006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2920376663903725</v>
+        <v>0.3065222350015709</v>
       </c>
       <c r="T84">
-        <v>5.062905590620454</v>
+        <v>5.360723566539304</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09032398278238009</v>
+        <v>0.08923574202596586</v>
       </c>
       <c r="W84">
-        <v>0.2145016048599148</v>
+        <v>0.2147582120302773</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3763499282599171</v>
+        <v>0.3718155917748578</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2303580959353972</v>
+        <v>0.2322580959353972</v>
       </c>
       <c r="C85">
-        <v>-725.6858546768055</v>
+        <v>-744.9341395340899</v>
       </c>
       <c r="D85">
-        <v>305.0341453231947</v>
+        <v>301.9258604659103</v>
       </c>
       <c r="E85">
-        <v>601.8200000000002</v>
+        <v>617.9600000000003</v>
       </c>
       <c r="F85">
-        <v>1339.62</v>
+        <v>1355.76</v>
       </c>
       <c r="G85">
         <v>308.9</v>
@@ -8263,37 +8263,37 @@
         <v>117.45</v>
       </c>
       <c r="M85">
-        <v>315.882396</v>
+        <v>319.6882080000001</v>
       </c>
       <c r="N85">
-        <v>-198.432396</v>
+        <v>-202.2382080000001</v>
       </c>
       <c r="O85">
-        <v>-47.62377504000001</v>
+        <v>-48.53716992000003</v>
       </c>
       <c r="P85">
-        <v>-150.80862096</v>
+        <v>-153.7010380800001</v>
       </c>
       <c r="Q85">
-        <v>-53.00862096000006</v>
+        <v>-55.90103808000009</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3065222350015709</v>
+        <v>0.3228173746891692</v>
       </c>
       <c r="T85">
-        <v>5.360723566539304</v>
+        <v>5.695768789448012</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08923574202596586</v>
+        <v>0.08817341176375199</v>
       </c>
       <c r="W85">
-        <v>0.2147582120302773</v>
+        <v>0.2150087095061073</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3718155917748578</v>
+        <v>0.3673892156822999</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2322580959353971</v>
+        <v>0.2341580959353972</v>
       </c>
       <c r="C86">
-        <v>-744.9341395340897</v>
+        <v>-764.1197168002878</v>
       </c>
       <c r="D86">
-        <v>301.9258604659103</v>
+        <v>298.880283199712</v>
       </c>
       <c r="E86">
-        <v>617.96</v>
+        <v>634.0999999999999</v>
       </c>
       <c r="F86">
-        <v>1355.76</v>
+        <v>1371.9</v>
       </c>
       <c r="G86">
         <v>308.9</v>
@@ -8345,37 +8345,37 @@
         <v>117.45</v>
       </c>
       <c r="M86">
-        <v>319.688208</v>
+        <v>323.49402</v>
       </c>
       <c r="N86">
-        <v>-202.238208</v>
+        <v>-206.04402</v>
       </c>
       <c r="O86">
-        <v>-48.53716992000001</v>
+        <v>-49.4505648</v>
       </c>
       <c r="P86">
-        <v>-153.70103808</v>
+        <v>-156.5934552</v>
       </c>
       <c r="Q86">
-        <v>-55.90103808000006</v>
+        <v>-58.79345520000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.322817374689169</v>
+        <v>0.3412851996684469</v>
       </c>
       <c r="T86">
-        <v>5.695768789448008</v>
+        <v>6.075486708744541</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.088173411763752</v>
+        <v>0.08713607750770787</v>
       </c>
       <c r="W86">
-        <v>0.2150087095061073</v>
+        <v>0.2152533129236825</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3673892156823</v>
+        <v>0.3630669896154495</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2341580959353972</v>
+        <v>0.2360580959353972</v>
       </c>
       <c r="C87">
-        <v>-764.1197168002878</v>
+        <v>-783.24446515114</v>
       </c>
       <c r="D87">
-        <v>298.880283199712</v>
+        <v>295.8955348488599</v>
       </c>
       <c r="E87">
-        <v>634.0999999999999</v>
+        <v>650.24</v>
       </c>
       <c r="F87">
-        <v>1371.9</v>
+        <v>1388.04</v>
       </c>
       <c r="G87">
         <v>308.9</v>
@@ -8427,37 +8427,37 @@
         <v>117.45</v>
       </c>
       <c r="M87">
-        <v>323.49402</v>
+        <v>327.299832</v>
       </c>
       <c r="N87">
-        <v>-206.04402</v>
+        <v>-209.849832</v>
       </c>
       <c r="O87">
-        <v>-49.4505648</v>
+        <v>-50.36395967999999</v>
       </c>
       <c r="P87">
-        <v>-156.5934552</v>
+        <v>-159.48587232</v>
       </c>
       <c r="Q87">
-        <v>-58.79345520000001</v>
+        <v>-61.68587232000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3412851996684469</v>
+        <v>0.3623912853590503</v>
       </c>
       <c r="T87">
-        <v>6.075486708744541</v>
+        <v>6.509450045083438</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08713607750770787</v>
+        <v>0.08612286730412987</v>
       </c>
       <c r="W87">
-        <v>0.2152533129236825</v>
+        <v>0.2154922278896862</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3630669896154495</v>
+        <v>0.3588452804338744</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2360580959353972</v>
+        <v>0.2379580959353972</v>
       </c>
       <c r="C88">
-        <v>-783.24446515114</v>
+        <v>-802.3101889593208</v>
       </c>
       <c r="D88">
-        <v>295.8955348488599</v>
+        <v>292.9698110406792</v>
       </c>
       <c r="E88">
-        <v>650.24</v>
+        <v>666.3800000000001</v>
       </c>
       <c r="F88">
-        <v>1388.04</v>
+        <v>1404.18</v>
       </c>
       <c r="G88">
         <v>308.9</v>
@@ -8509,37 +8509,37 @@
         <v>117.45</v>
       </c>
       <c r="M88">
-        <v>327.299832</v>
+        <v>331.105644</v>
       </c>
       <c r="N88">
-        <v>-209.849832</v>
+        <v>-213.6556440000001</v>
       </c>
       <c r="O88">
-        <v>-50.36395967999999</v>
+        <v>-51.27735456000001</v>
       </c>
       <c r="P88">
-        <v>-159.48587232</v>
+        <v>-162.37828944</v>
       </c>
       <c r="Q88">
-        <v>-61.68587232000002</v>
+        <v>-64.57828944000005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3623912853590503</v>
+        <v>0.3867444611559003</v>
       </c>
       <c r="T88">
-        <v>6.509450045083438</v>
+        <v>7.010176971628318</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08612286730412987</v>
+        <v>0.08513294928913985</v>
       </c>
       <c r="W88">
-        <v>0.2154922278896862</v>
+        <v>0.2157256505576208</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3588452804338744</v>
+        <v>0.3547206220380827</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2379580959353972</v>
+        <v>0.2398580959353972</v>
       </c>
       <c r="C89">
-        <v>-802.3101889593208</v>
+        <v>-821.3186219319012</v>
       </c>
       <c r="D89">
-        <v>292.9698110406792</v>
+        <v>290.1013780680987</v>
       </c>
       <c r="E89">
-        <v>666.3800000000001</v>
+        <v>682.52</v>
       </c>
       <c r="F89">
-        <v>1404.18</v>
+        <v>1420.32</v>
       </c>
       <c r="G89">
         <v>308.9</v>
@@ -8591,37 +8591,37 @@
         <v>117.45</v>
       </c>
       <c r="M89">
-        <v>331.105644</v>
+        <v>334.911456</v>
       </c>
       <c r="N89">
-        <v>-213.6556440000001</v>
+        <v>-217.461456</v>
       </c>
       <c r="O89">
-        <v>-51.27735456000001</v>
+        <v>-52.19074944</v>
       </c>
       <c r="P89">
-        <v>-162.37828944</v>
+        <v>-165.27070656</v>
       </c>
       <c r="Q89">
-        <v>-64.57828944000005</v>
+        <v>-67.47070656000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3867444611559003</v>
+        <v>0.4151564995855587</v>
       </c>
       <c r="T89">
-        <v>7.010176971628318</v>
+        <v>7.594358385930679</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08513294928913985</v>
+        <v>0.08416552941085419</v>
       </c>
       <c r="W89">
-        <v>0.2157256505576208</v>
+        <v>0.2159537681649206</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3547206220380827</v>
+        <v>0.3506897058785591</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2398580959353972</v>
+        <v>0.2417580959353972</v>
       </c>
       <c r="C90">
-        <v>-821.3186219319012</v>
+        <v>-840.2714305362016</v>
       </c>
       <c r="D90">
-        <v>290.1013780680987</v>
+        <v>287.2885694637985</v>
       </c>
       <c r="E90">
-        <v>682.52</v>
+        <v>698.6600000000001</v>
       </c>
       <c r="F90">
-        <v>1420.32</v>
+        <v>1436.46</v>
       </c>
       <c r="G90">
         <v>308.9</v>
@@ -8673,37 +8673,37 @@
         <v>117.45</v>
       </c>
       <c r="M90">
-        <v>334.911456</v>
+        <v>338.717268</v>
       </c>
       <c r="N90">
-        <v>-217.461456</v>
+        <v>-221.2672680000001</v>
       </c>
       <c r="O90">
-        <v>-52.19074944</v>
+        <v>-53.10414432000001</v>
       </c>
       <c r="P90">
-        <v>-165.27070656</v>
+        <v>-168.16312368</v>
       </c>
       <c r="Q90">
-        <v>-67.47070656000002</v>
+        <v>-70.36312368000006</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4151564995855587</v>
+        <v>0.4487343631842459</v>
       </c>
       <c r="T90">
-        <v>7.594358385930679</v>
+        <v>8.284754602833468</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08416552941085419</v>
+        <v>0.08321984930511424</v>
       </c>
       <c r="W90">
-        <v>0.2159537681649206</v>
+        <v>0.2161767595338541</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3506897058785591</v>
+        <v>0.3467493721046426</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2417580959353972</v>
+        <v>0.2436580959353972</v>
       </c>
       <c r="C91">
-        <v>-840.2714305362016</v>
+        <v>-859.1702172282533</v>
       </c>
       <c r="D91">
-        <v>287.2885694637985</v>
+        <v>284.529782771747</v>
       </c>
       <c r="E91">
-        <v>698.6600000000001</v>
+        <v>714.8000000000002</v>
       </c>
       <c r="F91">
-        <v>1436.46</v>
+        <v>1452.6</v>
       </c>
       <c r="G91">
         <v>308.9</v>
@@ -8755,37 +8755,37 @@
         <v>117.45</v>
       </c>
       <c r="M91">
-        <v>338.717268</v>
+        <v>342.52308</v>
       </c>
       <c r="N91">
-        <v>-221.2672680000001</v>
+        <v>-225.0730800000001</v>
       </c>
       <c r="O91">
-        <v>-53.10414432000001</v>
+        <v>-54.01753920000002</v>
       </c>
       <c r="P91">
-        <v>-168.16312368</v>
+        <v>-171.0555408</v>
       </c>
       <c r="Q91">
-        <v>-70.36312368000006</v>
+        <v>-73.25554080000006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4487343631842459</v>
+        <v>0.4890277995026704</v>
       </c>
       <c r="T91">
-        <v>8.284754602833468</v>
+        <v>9.113230063116815</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08321984930511424</v>
+        <v>0.0822951843128352</v>
       </c>
       <c r="W91">
-        <v>0.2161767595338541</v>
+        <v>0.2163947955390335</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3467493721046426</v>
+        <v>0.34289660130348</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2436580959353972</v>
+        <v>0.2455580959353972</v>
       </c>
       <c r="C92">
-        <v>-859.1702172282533</v>
+        <v>-878.016523497017</v>
       </c>
       <c r="D92">
-        <v>284.529782771747</v>
+        <v>281.8234765029831</v>
       </c>
       <c r="E92">
-        <v>714.8000000000002</v>
+        <v>730.9400000000001</v>
       </c>
       <c r="F92">
-        <v>1452.6</v>
+        <v>1468.74</v>
       </c>
       <c r="G92">
         <v>308.9</v>
@@ -8837,37 +8837,37 @@
         <v>117.45</v>
       </c>
       <c r="M92">
-        <v>342.52308</v>
+        <v>346.328892</v>
       </c>
       <c r="N92">
-        <v>-225.0730800000001</v>
+        <v>-228.878892</v>
       </c>
       <c r="O92">
-        <v>-54.01753920000002</v>
+        <v>-54.93093408</v>
       </c>
       <c r="P92">
-        <v>-171.0555408</v>
+        <v>-173.94795792</v>
       </c>
       <c r="Q92">
-        <v>-73.25554080000006</v>
+        <v>-76.14795792000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4890277995026704</v>
+        <v>0.538275332780745</v>
       </c>
       <c r="T92">
-        <v>9.113230063116815</v>
+        <v>10.12581118124091</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0822951843128352</v>
+        <v>0.08139084162807877</v>
       </c>
       <c r="W92">
-        <v>0.2163947955390335</v>
+        <v>0.216608039544099</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.34289660130348</v>
+        <v>0.3391285067836616</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2455580959353972</v>
+        <v>0.2474580959353972</v>
       </c>
       <c r="C93">
-        <v>-878.016523497017</v>
+        <v>-896.8118327365094</v>
       </c>
       <c r="D93">
-        <v>281.8234765029831</v>
+        <v>279.1681672634908</v>
       </c>
       <c r="E93">
-        <v>730.9400000000001</v>
+        <v>747.0800000000002</v>
       </c>
       <c r="F93">
-        <v>1468.74</v>
+        <v>1484.88</v>
       </c>
       <c r="G93">
         <v>308.9</v>
@@ -8919,37 +8919,37 @@
         <v>117.45</v>
       </c>
       <c r="M93">
-        <v>346.328892</v>
+        <v>350.1347040000001</v>
       </c>
       <c r="N93">
-        <v>-228.878892</v>
+        <v>-232.6847040000001</v>
       </c>
       <c r="O93">
-        <v>-54.93093408</v>
+        <v>-55.84432896000001</v>
       </c>
       <c r="P93">
-        <v>-173.94795792</v>
+        <v>-176.8403750400001</v>
       </c>
       <c r="Q93">
-        <v>-76.14795792000004</v>
+        <v>-79.04037504000007</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.538275332780745</v>
+        <v>0.5998347493783384</v>
       </c>
       <c r="T93">
-        <v>10.12581118124091</v>
+        <v>11.39153757889602</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08139084162807877</v>
+        <v>0.08050615856690399</v>
       </c>
       <c r="W93">
-        <v>0.216608039544099</v>
+        <v>0.216816647809924</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3391285067836616</v>
+        <v>0.3354423273621</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2474580959353972</v>
+        <v>0.2493580959353972</v>
       </c>
       <c r="C94">
-        <v>-896.8118327365094</v>
+        <v>-915.5575729570749</v>
       </c>
       <c r="D94">
-        <v>279.1681672634908</v>
+        <v>276.5624270429252</v>
       </c>
       <c r="E94">
-        <v>747.0800000000002</v>
+        <v>763.22</v>
       </c>
       <c r="F94">
-        <v>1484.88</v>
+        <v>1501.02</v>
       </c>
       <c r="G94">
         <v>308.9</v>
@@ -9001,37 +9001,37 @@
         <v>117.45</v>
       </c>
       <c r="M94">
-        <v>350.1347040000001</v>
+        <v>353.940516</v>
       </c>
       <c r="N94">
-        <v>-232.6847040000001</v>
+        <v>-236.490516</v>
       </c>
       <c r="O94">
-        <v>-55.84432896000001</v>
+        <v>-56.75772384</v>
       </c>
       <c r="P94">
-        <v>-176.8403750400001</v>
+        <v>-179.73279216</v>
       </c>
       <c r="Q94">
-        <v>-79.04037504000007</v>
+        <v>-81.93279216000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5998347493783384</v>
+        <v>0.678982570718101</v>
       </c>
       <c r="T94">
-        <v>11.39153757889602</v>
+        <v>13.01890009016689</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08050615856690399</v>
+        <v>0.07964050094790504</v>
       </c>
       <c r="W94">
-        <v>0.216816647809924</v>
+        <v>0.217020769876484</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3354423273621</v>
+        <v>0.331835420616271</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2493580959353972</v>
+        <v>0.2512580959353972</v>
       </c>
       <c r="C95">
-        <v>-915.5575729570749</v>
+        <v>-934.2551193462266</v>
       </c>
       <c r="D95">
-        <v>276.5624270429252</v>
+        <v>274.0048806537735</v>
       </c>
       <c r="E95">
-        <v>763.22</v>
+        <v>779.3600000000001</v>
       </c>
       <c r="F95">
-        <v>1501.02</v>
+        <v>1517.16</v>
       </c>
       <c r="G95">
         <v>308.9</v>
@@ -9083,37 +9083,37 @@
         <v>117.45</v>
       </c>
       <c r="M95">
-        <v>353.940516</v>
+        <v>357.7463280000001</v>
       </c>
       <c r="N95">
-        <v>-236.490516</v>
+        <v>-240.2963280000001</v>
       </c>
       <c r="O95">
-        <v>-56.75772384</v>
+        <v>-57.67111872000002</v>
       </c>
       <c r="P95">
-        <v>-179.73279216</v>
+        <v>-182.6252092800001</v>
       </c>
       <c r="Q95">
-        <v>-81.93279216000002</v>
+        <v>-84.82520928000008</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.678982570718101</v>
+        <v>0.7845129991711181</v>
       </c>
       <c r="T95">
-        <v>13.01890009016689</v>
+        <v>15.18871677186137</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07964050094790504</v>
+        <v>0.07879326157611879</v>
       </c>
       <c r="W95">
-        <v>0.217020769876484</v>
+        <v>0.2172205489203512</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.331835420616271</v>
+        <v>0.3283052565671617</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2512580959353972</v>
+        <v>0.2531580959353972</v>
       </c>
       <c r="C96">
-        <v>-934.2551193462266</v>
+        <v>-952.9057966886942</v>
       </c>
       <c r="D96">
-        <v>274.0048806537735</v>
+        <v>271.4942033113061</v>
       </c>
       <c r="E96">
-        <v>779.3600000000001</v>
+        <v>795.5000000000002</v>
       </c>
       <c r="F96">
-        <v>1517.16</v>
+        <v>1533.3</v>
       </c>
       <c r="G96">
         <v>308.9</v>
@@ -9165,37 +9165,37 @@
         <v>117.45</v>
       </c>
       <c r="M96">
-        <v>357.7463280000001</v>
+        <v>361.5521400000001</v>
       </c>
       <c r="N96">
-        <v>-240.2963280000001</v>
+        <v>-244.1021400000001</v>
       </c>
       <c r="O96">
-        <v>-57.67111872000002</v>
+        <v>-58.58451360000002</v>
       </c>
       <c r="P96">
-        <v>-182.6252092800001</v>
+        <v>-185.5176264000001</v>
       </c>
       <c r="Q96">
-        <v>-84.82520928000008</v>
+        <v>-87.71762640000009</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7845129991711181</v>
+        <v>0.9322555990053421</v>
       </c>
       <c r="T96">
-        <v>15.18871677186137</v>
+        <v>18.22646012623365</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07879326157611879</v>
+        <v>0.07796385882268596</v>
       </c>
       <c r="W96">
-        <v>0.2172205489203512</v>
+        <v>0.2174161220896107</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3283052565671617</v>
+        <v>0.3248494117611915</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2531580959353972</v>
+        <v>0.2550580959353972</v>
       </c>
       <c r="C97">
-        <v>-952.9057966886942</v>
+        <v>-971.5108816546335</v>
       </c>
       <c r="D97">
-        <v>271.4942033113061</v>
+        <v>269.0291183453666</v>
       </c>
       <c r="E97">
-        <v>795.5000000000002</v>
+        <v>811.6400000000001</v>
       </c>
       <c r="F97">
-        <v>1533.3</v>
+        <v>1549.44</v>
       </c>
       <c r="G97">
         <v>308.9</v>
@@ -9247,37 +9247,37 @@
         <v>117.45</v>
       </c>
       <c r="M97">
-        <v>361.5521400000001</v>
+        <v>365.357952</v>
       </c>
       <c r="N97">
-        <v>-244.1021400000001</v>
+        <v>-247.907952</v>
       </c>
       <c r="O97">
-        <v>-58.58451360000002</v>
+        <v>-59.49790848000001</v>
       </c>
       <c r="P97">
-        <v>-185.5176264000001</v>
+        <v>-188.41004352</v>
       </c>
       <c r="Q97">
-        <v>-87.71762640000009</v>
+        <v>-90.61004352000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9322555990053421</v>
+        <v>1.153869498756678</v>
       </c>
       <c r="T97">
-        <v>18.22646012623365</v>
+        <v>22.78307515779208</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07796385882268596</v>
+        <v>0.07715173529328299</v>
       </c>
       <c r="W97">
-        <v>0.2174161220896107</v>
+        <v>0.2176076208178439</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3248494117611915</v>
+        <v>0.3214655637220125</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2550580959353972</v>
+        <v>0.2569580959353972</v>
       </c>
       <c r="C98">
-        <v>-971.5108816546335</v>
+        <v>-990.0716049643028</v>
       </c>
       <c r="D98">
-        <v>269.0291183453666</v>
+        <v>266.6083950356972</v>
       </c>
       <c r="E98">
-        <v>811.6400000000001</v>
+        <v>827.78</v>
       </c>
       <c r="F98">
-        <v>1549.44</v>
+        <v>1565.58</v>
       </c>
       <c r="G98">
         <v>308.9</v>
@@ -9329,37 +9329,37 @@
         <v>117.45</v>
       </c>
       <c r="M98">
-        <v>365.357952</v>
+        <v>369.163764</v>
       </c>
       <c r="N98">
-        <v>-247.907952</v>
+        <v>-251.713764</v>
       </c>
       <c r="O98">
-        <v>-59.49790848000001</v>
+        <v>-60.41130336000001</v>
       </c>
       <c r="P98">
-        <v>-188.41004352</v>
+        <v>-191.30246064</v>
       </c>
       <c r="Q98">
-        <v>-90.61004352000003</v>
+        <v>-93.50246064000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.153869498756675</v>
+        <v>1.523225998342234</v>
       </c>
       <c r="T98">
-        <v>22.78307515779202</v>
+        <v>30.37743354372269</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07715173529328299</v>
+        <v>0.07635635657891925</v>
       </c>
       <c r="W98">
-        <v>0.2176076208178439</v>
+        <v>0.2177951711186908</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3214655637220125</v>
+        <v>0.3181514857454969</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2569580959353972</v>
+        <v>0.2588580959353972</v>
       </c>
       <c r="C99">
-        <v>-990.0716049643028</v>
+        <v>-1008.58915343691</v>
       </c>
       <c r="D99">
-        <v>266.6083950356972</v>
+        <v>264.2308465630899</v>
       </c>
       <c r="E99">
-        <v>827.78</v>
+        <v>843.9200000000001</v>
       </c>
       <c r="F99">
-        <v>1565.58</v>
+        <v>1581.72</v>
       </c>
       <c r="G99">
         <v>308.9</v>
@@ -9411,37 +9411,37 @@
         <v>117.45</v>
       </c>
       <c r="M99">
-        <v>369.163764</v>
+        <v>372.969576</v>
       </c>
       <c r="N99">
-        <v>-251.713764</v>
+        <v>-255.519576</v>
       </c>
       <c r="O99">
-        <v>-60.41130336000001</v>
+        <v>-61.32469824</v>
       </c>
       <c r="P99">
-        <v>-191.30246064</v>
+        <v>-194.19487776</v>
       </c>
       <c r="Q99">
-        <v>-93.50246064000004</v>
+        <v>-96.39487776000004</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.523225998342234</v>
+        <v>2.26193899751335</v>
       </c>
       <c r="T99">
-        <v>30.37743354372269</v>
+        <v>45.56615031558403</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07635635657891925</v>
+        <v>0.075577210083216</v>
       </c>
       <c r="W99">
-        <v>0.2177951711186908</v>
+        <v>0.2179788938623777</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3181514857454969</v>
+        <v>0.3149050420134</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2588580959353972</v>
+        <v>0.2607580959353972</v>
       </c>
       <c r="C100">
-        <v>-1008.58915343691</v>
+        <v>-1027.064671930806</v>
       </c>
       <c r="D100">
-        <v>264.2308465630899</v>
+        <v>261.8953280691936</v>
       </c>
       <c r="E100">
-        <v>843.9200000000001</v>
+        <v>860.0599999999999</v>
       </c>
       <c r="F100">
-        <v>1581.72</v>
+        <v>1597.86</v>
       </c>
       <c r="G100">
         <v>308.9</v>
@@ -9493,37 +9493,37 @@
         <v>117.45</v>
       </c>
       <c r="M100">
-        <v>372.969576</v>
+        <v>376.775388</v>
       </c>
       <c r="N100">
-        <v>-255.519576</v>
+        <v>-259.325388</v>
       </c>
       <c r="O100">
-        <v>-61.32469824</v>
+        <v>-62.23809311999999</v>
       </c>
       <c r="P100">
-        <v>-194.19487776</v>
+        <v>-197.08729488</v>
       </c>
       <c r="Q100">
-        <v>-96.39487776000004</v>
+        <v>-99.28729487999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.26193899751335</v>
+        <v>4.4780779950267</v>
       </c>
       <c r="T100">
-        <v>45.56615031558403</v>
+        <v>91.13230063116805</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.075577210083216</v>
+        <v>0.07481380392075929</v>
       </c>
       <c r="W100">
-        <v>0.2179788938623777</v>
+        <v>0.218158905035485</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3149050420134</v>
+        <v>0.3117241830031636</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2607580959353972</v>
-      </c>
-      <c r="C101">
-        <v>-1027.064671930806</v>
-      </c>
-      <c r="D101">
-        <v>261.8953280691936</v>
-      </c>
-      <c r="E101">
-        <v>860.0599999999999</v>
-      </c>
-      <c r="F101">
-        <v>1597.86</v>
-      </c>
-      <c r="G101">
-        <v>308.9</v>
-      </c>
-      <c r="H101">
-        <v>876.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>215.25</v>
-      </c>
-      <c r="K101">
-        <v>97.79999999999998</v>
-      </c>
-      <c r="L101">
-        <v>117.45</v>
-      </c>
-      <c r="M101">
-        <v>376.775388</v>
-      </c>
-      <c r="N101">
-        <v>-259.325388</v>
-      </c>
-      <c r="O101">
-        <v>-62.23809311999999</v>
-      </c>
-      <c r="P101">
-        <v>-197.08729488</v>
-      </c>
-      <c r="Q101">
-        <v>-99.28729487999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.4780779950267</v>
-      </c>
-      <c r="T101">
-        <v>91.13230063116805</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07481380392075929</v>
-      </c>
-      <c r="W101">
-        <v>0.218158905035485</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3117241830031636</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
